--- a/Space Station Aurora/Support_Excel.xlsx
+++ b/Space Station Aurora/Support_Excel.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Space Station Aurora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DBB5F4E-83E0-44B1-B952-DF6AC649AE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6143E9F6-1CAB-411E-920A-4E318E3C5E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
-    <sheet name="Bank_Statement" sheetId="3" r:id="rId2"/>
+    <sheet name="3DPrinting" sheetId="4" r:id="rId2"/>
+    <sheet name="Bank_Statement" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="67">
   <si>
     <t>Square cells</t>
   </si>
@@ -217,6 +218,27 @@
   </si>
   <si>
     <t>1262 0983 5681</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Depth</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Depth Diff</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mm3 = </t>
+  </si>
+  <si>
+    <t>ml</t>
   </si>
 </sst>
 </file>
@@ -226,7 +248,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -275,8 +297,16 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -295,8 +325,26 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="9">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -384,12 +432,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -450,17 +539,80 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1015,6 +1167,328 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A6A3ED-7961-4765-BEF1-5E3A399C6516}">
+  <dimension ref="B2:L15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="5.7109375" customWidth="1"/>
+    <col min="5" max="5" width="5.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B2" s="44">
+        <v>4</v>
+      </c>
+      <c r="C2" s="42">
+        <v>3</v>
+      </c>
+      <c r="D2" s="43"/>
+      <c r="E2" s="41">
+        <v>1</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>62</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>60</v>
+      </c>
+      <c r="I2" s="51" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="51" t="s">
+        <v>61</v>
+      </c>
+      <c r="K2" s="52" t="s">
+        <v>63</v>
+      </c>
+      <c r="L2" s="52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="44"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+      <c r="E3" s="41"/>
+      <c r="G3" s="53">
+        <v>1</v>
+      </c>
+      <c r="H3" s="53">
+        <v>10</v>
+      </c>
+      <c r="I3" s="53">
+        <v>55</v>
+      </c>
+      <c r="J3" s="53">
+        <v>35</v>
+      </c>
+      <c r="K3" s="53">
+        <f>J3-J4</f>
+        <v>5</v>
+      </c>
+      <c r="L3" s="53">
+        <f>H3*I3*K3*$D$15</f>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="44"/>
+      <c r="C4" s="40"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="41"/>
+      <c r="G4" s="53">
+        <v>2</v>
+      </c>
+      <c r="H4" s="53">
+        <v>10</v>
+      </c>
+      <c r="I4" s="53">
+        <v>55</v>
+      </c>
+      <c r="J4" s="53">
+        <v>30</v>
+      </c>
+      <c r="K4" s="53">
+        <f>J4-J5</f>
+        <v>5</v>
+      </c>
+      <c r="L4" s="53">
+        <f>H4*I4*K4*$D$15</f>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="44"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="41"/>
+      <c r="G5" s="54">
+        <v>3</v>
+      </c>
+      <c r="H5" s="54">
+        <v>10</v>
+      </c>
+      <c r="I5" s="54">
+        <v>40</v>
+      </c>
+      <c r="J5" s="54">
+        <v>25</v>
+      </c>
+      <c r="K5" s="54">
+        <f>J5-J6</f>
+        <v>5</v>
+      </c>
+      <c r="L5" s="54">
+        <f>H5*I5*K5*$D$15</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B6" s="44"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="41"/>
+      <c r="G6" s="37">
+        <v>4</v>
+      </c>
+      <c r="H6" s="37">
+        <v>10</v>
+      </c>
+      <c r="I6" s="37">
+        <v>55</v>
+      </c>
+      <c r="J6" s="37">
+        <v>20</v>
+      </c>
+      <c r="K6" s="37">
+        <f>J6-J7</f>
+        <v>5</v>
+      </c>
+      <c r="L6" s="37">
+        <f>H6*I6*K6*$D$15</f>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="44"/>
+      <c r="C7" s="45">
+        <v>5</v>
+      </c>
+      <c r="D7" s="44"/>
+      <c r="E7" s="41"/>
+      <c r="G7" s="37">
+        <v>5</v>
+      </c>
+      <c r="H7" s="37">
+        <v>10</v>
+      </c>
+      <c r="I7" s="37">
+        <v>40</v>
+      </c>
+      <c r="J7" s="37">
+        <v>15</v>
+      </c>
+      <c r="K7" s="37">
+        <f>J7-J8</f>
+        <v>5</v>
+      </c>
+      <c r="L7" s="37">
+        <f>H7*I7*K7*$D$15</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B8" s="38">
+        <v>6</v>
+      </c>
+      <c r="C8" s="45"/>
+      <c r="D8" s="44"/>
+      <c r="E8" s="41">
+        <v>2</v>
+      </c>
+      <c r="G8" s="36">
+        <v>6</v>
+      </c>
+      <c r="H8" s="36">
+        <v>10</v>
+      </c>
+      <c r="I8" s="36">
+        <v>55</v>
+      </c>
+      <c r="J8" s="36">
+        <v>10</v>
+      </c>
+      <c r="K8" s="36">
+        <f>J8-J9</f>
+        <v>5</v>
+      </c>
+      <c r="L8" s="36">
+        <f>H8*I8*K8*$D$15</f>
+        <v>2.75</v>
+      </c>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="38"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
+      <c r="E9" s="41"/>
+      <c r="G9" s="36">
+        <v>7</v>
+      </c>
+      <c r="H9" s="36">
+        <v>10</v>
+      </c>
+      <c r="I9" s="36">
+        <v>40</v>
+      </c>
+      <c r="J9" s="36">
+        <v>5</v>
+      </c>
+      <c r="K9" s="36">
+        <f>J9-J10</f>
+        <v>5</v>
+      </c>
+      <c r="L9" s="36">
+        <f>H9*I9*K9*$D$15</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="38"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B11" s="38"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="41"/>
+      <c r="G11" s="46">
+        <v>1</v>
+      </c>
+      <c r="H11" s="47">
+        <v>2</v>
+      </c>
+      <c r="I11" s="34">
+        <f>L3+L4</f>
+        <v>5.5</v>
+      </c>
+      <c r="J11" s="34">
+        <f>I11</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="38"/>
+      <c r="C12" s="39">
+        <v>7</v>
+      </c>
+      <c r="D12" s="38"/>
+      <c r="E12" s="41"/>
+      <c r="G12" s="48">
+        <v>3</v>
+      </c>
+      <c r="H12" s="42"/>
+      <c r="I12" s="34">
+        <f>L5</f>
+        <v>2</v>
+      </c>
+      <c r="J12" s="34">
+        <f>J11+I12</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="41"/>
+      <c r="G13" s="49">
+        <v>4</v>
+      </c>
+      <c r="H13" s="50">
+        <v>5</v>
+      </c>
+      <c r="I13" s="34">
+        <f>L6+L7</f>
+        <v>4.75</v>
+      </c>
+      <c r="J13" s="34">
+        <f>J12+I13</f>
+        <v>12.25</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B15" s="35">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="35">
+        <v>1E-3</v>
+      </c>
+      <c r="E15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E2:E7"/>
+    <mergeCell ref="E8:E13"/>
+    <mergeCell ref="C12:D13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C2:D3"/>
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="B8:B13"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECC840A-39FE-48EF-AC39-316EEDAB0404}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -1143,11 +1617,11 @@
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="30" t="s">
+      <c r="B16" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="31"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9">
         <v>34.56</v>
@@ -1161,11 +1635,11 @@
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>100000</v>
@@ -1179,11 +1653,11 @@
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
       <c r="E18" s="9">
         <v>1000000</v>
       </c>
@@ -1199,11 +1673,11 @@
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>20</v>
@@ -1217,11 +1691,11 @@
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="30" t="s">
+      <c r="B20" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9">
         <v>29.12</v>
@@ -1235,11 +1709,11 @@
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>46.73</v>
@@ -1254,11 +1728,11 @@
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="30"/>
-      <c r="D22" s="30"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="31"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9">
         <v>35.67</v>
@@ -1273,11 +1747,11 @@
       <c r="A23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="31"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
       <c r="E23" s="12">
         <v>3421.98</v>
       </c>
@@ -1293,11 +1767,11 @@
       <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="30" t="s">
+      <c r="B24" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="31"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9">
         <v>200000</v>
@@ -1311,11 +1785,11 @@
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>150000</v>
@@ -1329,11 +1803,11 @@
       <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="30" t="s">
+      <c r="B26" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
         <v>20</v>
@@ -1347,11 +1821,11 @@
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="31"/>
+      <c r="C27" s="30"/>
+      <c r="D27" s="30"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>45.23</v>
@@ -1365,11 +1839,11 @@
       <c r="A28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="30" t="s">
+      <c r="B28" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="31"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
         <f>1.05*200000</f>
@@ -1384,11 +1858,11 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12">
         <f>1.05*100000</f>
@@ -1403,11 +1877,11 @@
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="30" t="s">
+      <c r="B30" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="30"/>
-      <c r="D30" s="30"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
       <c r="E30" s="9">
         <v>3421.98</v>
       </c>
@@ -1423,11 +1897,11 @@
       <c r="A31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="C31" s="30"/>
+      <c r="D31" s="30"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>204.73</v>
@@ -1441,11 +1915,11 @@
       <c r="A32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="30" t="s">
+      <c r="B32" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9">
         <v>63.29</v>
@@ -1459,11 +1933,11 @@
       <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="C33" s="30"/>
+      <c r="D33" s="30"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>100000</v>
@@ -1477,11 +1951,11 @@
       <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="30" t="s">
+      <c r="B34" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="30"/>
-      <c r="D34" s="30"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9">
         <v>100000</v>
@@ -1495,11 +1969,11 @@
       <c r="A35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="C35" s="30"/>
+      <c r="D35" s="30"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>86.7</v>
@@ -1568,6 +2042,14 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B27:D27"/>
@@ -1582,14 +2064,6 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Space Station Aurora/Support_Excel.xlsx
+++ b/Space Station Aurora/Support_Excel.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Space Station Aurora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6143E9F6-1CAB-411E-920A-4E318E3C5E24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4AA22D-D9CC-462A-8298-BA7786246F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
     <sheet name="3DPrinting" sheetId="4" r:id="rId2"/>
-    <sheet name="Bank_Statement" sheetId="3" r:id="rId3"/>
+    <sheet name="Electronic_Puzzle" sheetId="5" r:id="rId3"/>
+    <sheet name="Electronic_Pins" sheetId="6" r:id="rId4"/>
+    <sheet name="Bank_Statement" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Electronic_Pins!$A$1:$D$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="226">
   <si>
     <t>Square cells</t>
   </si>
@@ -239,6 +244,483 @@
   </si>
   <si>
     <t>ml</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>ABX00033</t>
+  </si>
+  <si>
+    <t>Arduino Nano Every With Headers</t>
+  </si>
+  <si>
+    <t>Control board for the puzzle</t>
+  </si>
+  <si>
+    <t>DKS-SOLDERBREAD-02-ND</t>
+  </si>
+  <si>
+    <t>BREADBOARD GENERAL PURPOSE PTH</t>
+  </si>
+  <si>
+    <t>Solderboard to connect elements (power, ground…)</t>
+  </si>
+  <si>
+    <t>Item Type</t>
+  </si>
+  <si>
+    <t>Control Board</t>
+  </si>
+  <si>
+    <t>Solderboard</t>
+  </si>
+  <si>
+    <t>PDB181-E420K-103A2-ND</t>
+  </si>
+  <si>
+    <t>POT 10K OHM 1/10W CARBON LOG</t>
+  </si>
+  <si>
+    <t>Potentiometer</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>2-position switch</t>
+  </si>
+  <si>
+    <t>RA11131100-ND</t>
+  </si>
+  <si>
+    <t>SWITCH ROCKER SPST 10A 125V</t>
+  </si>
+  <si>
+    <t>For another puzzle</t>
+  </si>
+  <si>
+    <t>SW GP560/20-25 AT</t>
+  </si>
+  <si>
+    <t>Glass Body Reed Switch SPST-NO 10 ~ 50AT Operate Range 10VA 1A (AC/DC) 125 V Through Hole</t>
+  </si>
+  <si>
+    <t>Reed</t>
+  </si>
+  <si>
+    <t>Detects magnets, standard escape room mechanism (piece with magnet in it)</t>
+  </si>
+  <si>
+    <t>25ZLH470MEFC10X12.5</t>
+  </si>
+  <si>
+    <t>CAP ALUM 470UF 20% 25V RADIAL TH</t>
+  </si>
+  <si>
+    <t>Capacitors</t>
+  </si>
+  <si>
+    <t>Decoupling Capacitors for servos</t>
+  </si>
+  <si>
+    <t>Dials - Need about 10kΩ + Solder Lugs</t>
+  </si>
+  <si>
+    <t>On/off switches</t>
+  </si>
+  <si>
+    <t>1738-1300-ND</t>
+  </si>
+  <si>
+    <t>SERVOMOTOR RC 4.8-6V</t>
+  </si>
+  <si>
+    <t>Servo motors</t>
+  </si>
+  <si>
+    <t>Servo motors to open/close compartments</t>
+  </si>
+  <si>
+    <t>1528-2951-ND</t>
+  </si>
+  <si>
+    <t>KIT LED ROUND 3MM T1 TH 25 PCS</t>
+  </si>
+  <si>
+    <t>LED lights</t>
+  </si>
+  <si>
+    <t>Colour LEDs for power ON, Error and other indications</t>
+  </si>
+  <si>
+    <t>1528-1136-ND</t>
+  </si>
+  <si>
+    <t>SWITCH KEYPAD 12KEY NON-ILLUM</t>
+  </si>
+  <si>
+    <t>Keypad</t>
+  </si>
+  <si>
+    <t>1568-15464-ND</t>
+  </si>
+  <si>
+    <t>CBL MCR B RCPT-MCR B PLUG 0.5'</t>
+  </si>
+  <si>
+    <t>Power Supply</t>
+  </si>
+  <si>
+    <t>USB Power supply. Need external power bank plugged in</t>
+  </si>
+  <si>
+    <t>Keypad (0 to 9, *, #)</t>
+  </si>
+  <si>
+    <t>1528-4482-ND</t>
+  </si>
+  <si>
+    <t>SILICONE M-M JUMPER 200MM X 40</t>
+  </si>
+  <si>
+    <t>Jumper Wire</t>
+  </si>
+  <si>
+    <t>Wires to connect all elements</t>
+  </si>
+  <si>
+    <t>433-1028-ND</t>
+  </si>
+  <si>
+    <t>BUZZER MAGNETIC 5V 12MM TH</t>
+  </si>
+  <si>
+    <t>Buzzer</t>
+  </si>
+  <si>
+    <t>Pin</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>What it does</t>
+  </si>
+  <si>
+    <t>Digital</t>
+  </si>
+  <si>
+    <t>D13</t>
+  </si>
+  <si>
+    <t>Standard digital pin. Also used for the built-in onboard LED.</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>3.3V out</t>
+  </si>
+  <si>
+    <t>Provides 3.3V power to other components.</t>
+  </si>
+  <si>
+    <t>Analog</t>
+  </si>
+  <si>
+    <t>AREF</t>
+  </si>
+  <si>
+    <t>Sets a custom maximum voltage for analog readings. Rarely needed — can be used as a digital pin.</t>
+  </si>
+  <si>
+    <t>A0</t>
+  </si>
+  <si>
+    <t>Reads analog voltage (0–5V). Can also output a variable voltage. Usable as digital pin.</t>
+  </si>
+  <si>
+    <t>A1</t>
+  </si>
+  <si>
+    <t>Reads analog voltage (0–5V). Usable as digital pin.</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A4</t>
+  </si>
+  <si>
+    <t>Reads analog voltage. Also used for I2C data communication (connecting sensors/displays). Usable as digital pin.</t>
+  </si>
+  <si>
+    <t>A5</t>
+  </si>
+  <si>
+    <t>Reads analog voltage. Also used for I2C clock communication. Usable as digital pin.</t>
+  </si>
+  <si>
+    <t>A6</t>
+  </si>
+  <si>
+    <t>Reads analog voltage only — cannot be used as a digital pin.</t>
+  </si>
+  <si>
+    <t>A7</t>
+  </si>
+  <si>
+    <t>5V out</t>
+  </si>
+  <si>
+    <t>Provides 5V power to other components.</t>
+  </si>
+  <si>
+    <t>Reset</t>
+  </si>
+  <si>
+    <t>Restarting the board when pulled to ground. Avoid using for anything else.</t>
+  </si>
+  <si>
+    <t>GND</t>
+  </si>
+  <si>
+    <t>Ground — the negative/return connection for all components.</t>
+  </si>
+  <si>
+    <t>VIN</t>
+  </si>
+  <si>
+    <t>Power input — supply 7–12V here to power the board externally (instead of USB).</t>
+  </si>
+  <si>
+    <t>D1 / TX</t>
+  </si>
+  <si>
+    <t>Digital pin. Also transmits data over USB serial. Avoid if using the serial monitor.</t>
+  </si>
+  <si>
+    <t>D0 / RX</t>
+  </si>
+  <si>
+    <t>Digital pin. Also receives data over USB serial. Avoid if using the serial monitor.</t>
+  </si>
+  <si>
+    <t>Reset (2nd)</t>
+  </si>
+  <si>
+    <t>Same as pin 13 — second reset connection point on the board.</t>
+  </si>
+  <si>
+    <t>GND (2nd)</t>
+  </si>
+  <si>
+    <t>Second ground connection — same as pin 14.</t>
+  </si>
+  <si>
+    <t>D2</t>
+  </si>
+  <si>
+    <t>Standard digital pin.</t>
+  </si>
+  <si>
+    <t>D3 ⚡</t>
+  </si>
+  <si>
+    <t>Digital pin. Supports PWM — can simulate variable power output (e.g. LED dimming, motor speed).</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>D5 ⚡</t>
+  </si>
+  <si>
+    <t>Digital pin with PWM support.</t>
+  </si>
+  <si>
+    <t>D6 ⚡</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>D8</t>
+  </si>
+  <si>
+    <t>D9 ⚡</t>
+  </si>
+  <si>
+    <t>D10 ⚡</t>
+  </si>
+  <si>
+    <t>D11 ⚡</t>
+  </si>
+  <si>
+    <t>Digital pin with PWM support. Also used for SPI communication (sending data to devices like displays).</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>Digital pin. Also used for SPI communication (receiving data).</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Wire</t>
+  </si>
+  <si>
+    <t>Connects to</t>
+  </si>
+  <si>
+    <t>servo1</t>
+  </si>
+  <si>
+    <t>Signal (orange)</t>
+  </si>
+  <si>
+    <t>D5</t>
+  </si>
+  <si>
+    <t>PWM signal</t>
+  </si>
+  <si>
+    <t>Power (red)</t>
+  </si>
+  <si>
+    <t>5V rail</t>
+  </si>
+  <si>
+    <t>Ground (brown)</t>
+  </si>
+  <si>
+    <t>GND rail</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>servo2</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>led1 (yellow)</t>
+  </si>
+  <si>
+    <t>Anode (+)</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Cathode (−)</t>
+  </si>
+  <si>
+    <t>led2 (green)</t>
+  </si>
+  <si>
+    <t>R1</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>D9</t>
+  </si>
+  <si>
+    <t>C1</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>D6</t>
+  </si>
+  <si>
+    <t>pot2</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Middle (wiper)</t>
+  </si>
+  <si>
+    <t>Analog signal</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>pot4</t>
+  </si>
+  <si>
+    <t>pot3</t>
+  </si>
+  <si>
+    <t>sw1</t>
+  </si>
+  <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>One outer pin</t>
+  </si>
+  <si>
+    <t>Other outer pin</t>
+  </si>
+  <si>
+    <t>Not connected</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>sw2</t>
+  </si>
+  <si>
+    <t>keypad</t>
+  </si>
+  <si>
+    <t>v</t>
+  </si>
+  <si>
+    <t>A0 → resistor → anode</t>
+  </si>
+  <si>
+    <t>A1 → resistor → anode</t>
   </si>
 </sst>
 </file>
@@ -248,7 +730,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -305,8 +787,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,6 +856,60 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -478,7 +1048,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -539,40 +1109,64 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -587,33 +1181,85 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1176,297 +1822,297 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="44">
+      <c r="B2" s="52">
         <v>4</v>
       </c>
-      <c r="C2" s="42">
+      <c r="C2" s="50">
         <v>3</v>
       </c>
-      <c r="D2" s="43"/>
-      <c r="E2" s="41">
+      <c r="D2" s="51"/>
+      <c r="E2" s="46">
         <v>1</v>
       </c>
-      <c r="G2" s="51" t="s">
+      <c r="G2" s="34" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="51" t="s">
+      <c r="H2" s="34" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="K2" s="52" t="s">
+      <c r="K2" s="34" t="s">
         <v>63</v>
       </c>
-      <c r="L2" s="52" t="s">
+      <c r="L2" s="34" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="44"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="43"/>
-      <c r="E3" s="41"/>
-      <c r="G3" s="53">
+      <c r="B3" s="52"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="46"/>
+      <c r="G3" s="40">
         <v>1</v>
       </c>
-      <c r="H3" s="53">
+      <c r="H3" s="40">
         <v>10</v>
       </c>
-      <c r="I3" s="53">
+      <c r="I3" s="40">
         <v>55</v>
       </c>
-      <c r="J3" s="53">
+      <c r="J3" s="40">
         <v>35</v>
       </c>
-      <c r="K3" s="53">
-        <f>J3-J4</f>
+      <c r="K3" s="40">
+        <f t="shared" ref="K3:K9" si="0">J3-J4</f>
         <v>5</v>
       </c>
-      <c r="L3" s="53">
-        <f>H3*I3*K3*$D$15</f>
+      <c r="L3" s="40">
+        <f t="shared" ref="L3:L9" si="1">H3*I3*K3*$D$15</f>
         <v>2.75</v>
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="44"/>
-      <c r="C4" s="40"/>
-      <c r="D4" s="40"/>
-      <c r="E4" s="41"/>
-      <c r="G4" s="53">
+      <c r="B4" s="52"/>
+      <c r="C4" s="35"/>
+      <c r="D4" s="35"/>
+      <c r="E4" s="46"/>
+      <c r="G4" s="40">
         <v>2</v>
       </c>
-      <c r="H4" s="53">
+      <c r="H4" s="40">
         <v>10</v>
       </c>
-      <c r="I4" s="53">
+      <c r="I4" s="40">
         <v>55</v>
       </c>
-      <c r="J4" s="53">
+      <c r="J4" s="40">
         <v>30</v>
       </c>
-      <c r="K4" s="53">
-        <f>J4-J5</f>
+      <c r="K4" s="40">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L4" s="53">
-        <f>H4*I4*K4*$D$15</f>
+      <c r="L4" s="40">
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="44"/>
-      <c r="C5" s="40"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="41"/>
-      <c r="G5" s="54">
+      <c r="B5" s="52"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="46"/>
+      <c r="G5" s="41">
         <v>3</v>
       </c>
-      <c r="H5" s="54">
+      <c r="H5" s="41">
         <v>10</v>
       </c>
-      <c r="I5" s="54">
+      <c r="I5" s="41">
         <v>40</v>
       </c>
-      <c r="J5" s="54">
+      <c r="J5" s="41">
         <v>25</v>
       </c>
-      <c r="K5" s="54">
-        <f>J5-J6</f>
+      <c r="K5" s="41">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="54">
-        <f>H5*I5*K5*$D$15</f>
+      <c r="L5" s="41">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="44"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="41"/>
-      <c r="G6" s="37">
+      <c r="B6" s="52"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
+      <c r="E6" s="46"/>
+      <c r="G6" s="33">
         <v>4</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="33">
         <v>10</v>
       </c>
-      <c r="I6" s="37">
+      <c r="I6" s="33">
         <v>55</v>
       </c>
-      <c r="J6" s="37">
+      <c r="J6" s="33">
         <v>20</v>
       </c>
-      <c r="K6" s="37">
-        <f>J6-J7</f>
+      <c r="K6" s="33">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L6" s="37">
-        <f>H6*I6*K6*$D$15</f>
+      <c r="L6" s="33">
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="44"/>
-      <c r="C7" s="45">
+      <c r="B7" s="52"/>
+      <c r="C7" s="53">
         <v>5</v>
       </c>
-      <c r="D7" s="44"/>
-      <c r="E7" s="41"/>
-      <c r="G7" s="37">
+      <c r="D7" s="52"/>
+      <c r="E7" s="46"/>
+      <c r="G7" s="33">
         <v>5</v>
       </c>
-      <c r="H7" s="37">
+      <c r="H7" s="33">
         <v>10</v>
       </c>
-      <c r="I7" s="37">
+      <c r="I7" s="33">
         <v>40</v>
       </c>
-      <c r="J7" s="37">
+      <c r="J7" s="33">
         <v>15</v>
       </c>
-      <c r="K7" s="37">
-        <f>J7-J8</f>
+      <c r="K7" s="33">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L7" s="37">
-        <f>H7*I7*K7*$D$15</f>
+      <c r="L7" s="33">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="38">
+      <c r="B8" s="48">
         <v>6</v>
       </c>
-      <c r="C8" s="45"/>
-      <c r="D8" s="44"/>
-      <c r="E8" s="41">
+      <c r="C8" s="53"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="46">
         <v>2</v>
       </c>
-      <c r="G8" s="36">
+      <c r="G8" s="32">
         <v>6</v>
       </c>
-      <c r="H8" s="36">
+      <c r="H8" s="32">
         <v>10</v>
       </c>
-      <c r="I8" s="36">
+      <c r="I8" s="32">
         <v>55</v>
       </c>
-      <c r="J8" s="36">
+      <c r="J8" s="32">
         <v>10</v>
       </c>
-      <c r="K8" s="36">
-        <f>J8-J9</f>
+      <c r="K8" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L8" s="36">
-        <f>H8*I8*K8*$D$15</f>
+      <c r="L8" s="32">
+        <f t="shared" si="1"/>
         <v>2.75</v>
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="38"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="41"/>
-      <c r="G9" s="36">
+      <c r="B9" s="48"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="46"/>
+      <c r="G9" s="32">
         <v>7</v>
       </c>
-      <c r="H9" s="36">
+      <c r="H9" s="32">
         <v>10</v>
       </c>
-      <c r="I9" s="36">
+      <c r="I9" s="32">
         <v>40</v>
       </c>
-      <c r="J9" s="36">
+      <c r="J9" s="32">
         <v>5</v>
       </c>
-      <c r="K9" s="36">
-        <f>J9-J10</f>
+      <c r="K9" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L9" s="36">
-        <f>H9*I9*K9*$D$15</f>
+      <c r="L9" s="32">
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="38"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="41"/>
+      <c r="B10" s="48"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="46"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="38"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
-      <c r="E11" s="41"/>
-      <c r="G11" s="46">
+      <c r="B11" s="48"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="46"/>
+      <c r="G11" s="37">
         <v>1</v>
       </c>
-      <c r="H11" s="47">
+      <c r="H11" s="38">
         <v>2</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="30">
         <f>L3+L4</f>
         <v>5.5</v>
       </c>
-      <c r="J11" s="34">
+      <c r="J11" s="30">
         <f>I11</f>
         <v>5.5</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="38"/>
-      <c r="C12" s="39">
+      <c r="B12" s="48"/>
+      <c r="C12" s="47">
         <v>7</v>
       </c>
-      <c r="D12" s="38"/>
-      <c r="E12" s="41"/>
-      <c r="G12" s="48">
+      <c r="D12" s="48"/>
+      <c r="E12" s="46"/>
+      <c r="G12" s="49">
         <v>3</v>
       </c>
-      <c r="H12" s="42"/>
-      <c r="I12" s="34">
+      <c r="H12" s="50"/>
+      <c r="I12" s="30">
         <f>L5</f>
         <v>2</v>
       </c>
-      <c r="J12" s="34">
+      <c r="J12" s="30">
         <f>J11+I12</f>
         <v>7.5</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="38"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="41"/>
-      <c r="G13" s="49">
+      <c r="B13" s="48"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="46"/>
+      <c r="G13" s="39">
         <v>4</v>
       </c>
-      <c r="H13" s="50">
+      <c r="H13" s="36">
         <v>5</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="30">
         <f>L6+L7</f>
         <v>4.75</v>
       </c>
-      <c r="J13" s="34">
+      <c r="J13" s="30">
         <f>J12+I13</f>
         <v>12.25</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="35">
+      <c r="B15" s="31">
         <v>1</v>
       </c>
       <c r="C15" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="31">
         <v>1E-3</v>
       </c>
       <c r="E15" t="s">
@@ -1475,20 +2121,1415 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="B2:B7"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="B8:B13"/>
     <mergeCell ref="E2:E7"/>
     <mergeCell ref="E8:E13"/>
     <mergeCell ref="C12:D13"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="C2:D3"/>
-    <mergeCell ref="B2:B7"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="B8:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A425A6-023C-40DB-9218-09DD8A4595A3}">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="21" customWidth="1"/>
+    <col min="7" max="7" width="80.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="F1" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="55" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="56">
+        <v>1</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2" s="57">
+        <v>21.7</v>
+      </c>
+      <c r="F2" s="57">
+        <f>B2*E2</f>
+        <v>21.7</v>
+      </c>
+      <c r="G2" s="55" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="55" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="56">
+        <v>1</v>
+      </c>
+      <c r="C3" s="55" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" s="57">
+        <v>5.08</v>
+      </c>
+      <c r="F3" s="57">
+        <f t="shared" ref="F3:F11" si="0">B3*E3</f>
+        <v>5.08</v>
+      </c>
+      <c r="G3" s="55" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="55" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="56">
+        <v>4</v>
+      </c>
+      <c r="C4" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="55" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="57">
+        <v>1.88</v>
+      </c>
+      <c r="F4" s="57">
+        <f t="shared" si="0"/>
+        <v>7.52</v>
+      </c>
+      <c r="G4" s="55" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="56">
+        <v>3</v>
+      </c>
+      <c r="C5" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="57">
+        <v>0.93</v>
+      </c>
+      <c r="F5" s="57">
+        <f t="shared" si="0"/>
+        <v>2.79</v>
+      </c>
+      <c r="G5" s="55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B6" s="56">
+        <v>2</v>
+      </c>
+      <c r="C6" s="55" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="57">
+        <v>0.79</v>
+      </c>
+      <c r="F6" s="57">
+        <f t="shared" si="0"/>
+        <v>1.58</v>
+      </c>
+      <c r="G6" s="55" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="55" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="56">
+        <v>2</v>
+      </c>
+      <c r="C7" s="55" t="s">
+        <v>100</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="57">
+        <v>6.21</v>
+      </c>
+      <c r="F7" s="57">
+        <f t="shared" si="0"/>
+        <v>12.42</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="56">
+        <v>1</v>
+      </c>
+      <c r="C8" s="55" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="57">
+        <v>4.58</v>
+      </c>
+      <c r="F8" s="57">
+        <f t="shared" si="0"/>
+        <v>4.58</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="56">
+        <v>1</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="57">
+        <v>6.13</v>
+      </c>
+      <c r="F9" s="57">
+        <f t="shared" si="0"/>
+        <v>6.13</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="56">
+        <v>1</v>
+      </c>
+      <c r="C10" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="D10" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="E10" s="57">
+        <v>6.89</v>
+      </c>
+      <c r="F10" s="57">
+        <f t="shared" si="0"/>
+        <v>6.89</v>
+      </c>
+      <c r="G10" s="55" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="B11" s="56">
+        <v>1</v>
+      </c>
+      <c r="C11" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="57">
+        <v>14.49</v>
+      </c>
+      <c r="F11" s="57">
+        <f t="shared" si="0"/>
+        <v>14.49</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="55"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="55"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="55"/>
+      <c r="B13" s="56"/>
+      <c r="C13" s="55"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="55"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="55"/>
+      <c r="B14" s="56"/>
+      <c r="C14" s="55"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="55"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F15" s="58">
+        <f>SUM(F2:F14)</f>
+        <v>83.179999999999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="54" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="54" t="s">
+        <v>78</v>
+      </c>
+      <c r="E19" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>84</v>
+      </c>
+      <c r="G19" s="54" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="B20" s="56">
+        <v>4</v>
+      </c>
+      <c r="C20" s="55" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>91</v>
+      </c>
+      <c r="E20" s="57">
+        <v>0.89</v>
+      </c>
+      <c r="F20" s="57"/>
+      <c r="G20" s="55" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" s="56">
+        <v>1</v>
+      </c>
+      <c r="C21" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="57">
+        <v>1.07</v>
+      </c>
+      <c r="F21" s="57"/>
+      <c r="G21" s="55"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="55"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="55"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="55"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="55"/>
+      <c r="D23" s="55"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="55"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="55"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="55"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="55"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="55"/>
+      <c r="D25" s="55"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="55"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="55"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="55"/>
+      <c r="D26" s="55"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="55"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="55"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="55"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="55"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="55"/>
+      <c r="D28" s="55"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="55"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="55"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="55"/>
+      <c r="D29" s="55"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="55"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="55"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="55"/>
+      <c r="D30" s="55"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="55"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="55"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="55"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="55"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="55"/>
+      <c r="D32" s="55"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="55"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="55"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="55"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F34" s="58">
+        <f>SUM(F20:F33)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77460AD8-8752-4C96-A515-3367E229774E}">
+  <dimension ref="A1:J33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="30"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="90.42578125" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="59" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>123</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="59" t="s">
+        <v>124</v>
+      </c>
+      <c r="G1" s="59" t="s">
+        <v>179</v>
+      </c>
+      <c r="H1" s="59" t="s">
+        <v>180</v>
+      </c>
+      <c r="I1" s="59" t="s">
+        <v>181</v>
+      </c>
+      <c r="J1" s="59" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="64">
+        <v>1</v>
+      </c>
+      <c r="B2" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="D2" s="63" t="s">
+        <v>127</v>
+      </c>
+      <c r="G2" s="66" t="s">
+        <v>182</v>
+      </c>
+      <c r="H2" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="I2" s="67" t="s">
+        <v>203</v>
+      </c>
+      <c r="J2" s="68" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="64">
+        <v>2</v>
+      </c>
+      <c r="B3" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="63" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>182</v>
+      </c>
+      <c r="H3" s="70" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="J3" s="71" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="64">
+        <v>3</v>
+      </c>
+      <c r="B4" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="63" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="72" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="74" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="64">
+        <v>4</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="63" t="s">
+        <v>135</v>
+      </c>
+      <c r="E5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G5" s="66" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="67" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="67" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" s="68" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="64">
+        <v>5</v>
+      </c>
+      <c r="B6" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" t="s">
+        <v>223</v>
+      </c>
+      <c r="G6" s="69" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="70" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="70" t="s">
+        <v>187</v>
+      </c>
+      <c r="J6" s="71" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="64">
+        <v>6</v>
+      </c>
+      <c r="B7" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" t="s">
+        <v>223</v>
+      </c>
+      <c r="G7" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="73" t="s">
+        <v>188</v>
+      </c>
+      <c r="I7" s="73" t="s">
+        <v>189</v>
+      </c>
+      <c r="J7" s="74" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="64">
+        <v>7</v>
+      </c>
+      <c r="B8" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="E8" t="s">
+        <v>223</v>
+      </c>
+      <c r="G8" s="87" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="75" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" s="75" t="s">
+        <v>224</v>
+      </c>
+      <c r="J8" s="88" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="64">
+        <v>8</v>
+      </c>
+      <c r="B9" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="63" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="89" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="76" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9" s="76" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="90" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="64">
+        <v>9</v>
+      </c>
+      <c r="B10" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="63" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
+        <v>223</v>
+      </c>
+      <c r="G10" s="89" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="76" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="76" t="s">
+        <v>225</v>
+      </c>
+      <c r="J10" s="90" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="64">
+        <v>10</v>
+      </c>
+      <c r="B11" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="E11" t="s">
+        <v>223</v>
+      </c>
+      <c r="G11" s="91" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="77" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" s="77" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="92" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="64">
+        <v>11</v>
+      </c>
+      <c r="B12" s="62" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="63" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="78" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="79" t="s">
+        <v>198</v>
+      </c>
+      <c r="I12" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="J12" s="80" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="64">
+        <v>12</v>
+      </c>
+      <c r="B13" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="63" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="82" t="s">
+        <v>199</v>
+      </c>
+      <c r="I13" s="82" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="64">
+        <v>13</v>
+      </c>
+      <c r="B14" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H14" s="82" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="82" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="64">
+        <v>14</v>
+      </c>
+      <c r="B15" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="63" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H15" s="82" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="82" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="64">
+        <v>15</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="63" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H16" s="82" t="s">
+        <v>204</v>
+      </c>
+      <c r="I16" s="82" t="s">
+        <v>207</v>
+      </c>
+      <c r="J16" s="83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="64">
+        <v>16</v>
+      </c>
+      <c r="B17" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="81" t="s">
+        <v>222</v>
+      </c>
+      <c r="H17" s="82" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="82" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="83" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="64">
+        <v>17</v>
+      </c>
+      <c r="B18" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="63" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="84" t="s">
+        <v>222</v>
+      </c>
+      <c r="H18" s="85" t="s">
+        <v>206</v>
+      </c>
+      <c r="I18" s="85" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="86" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="64">
+        <v>18</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="63" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="93" t="s">
+        <v>208</v>
+      </c>
+      <c r="H19" s="94" t="s">
+        <v>209</v>
+      </c>
+      <c r="I19" s="94" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="64">
+        <v>19</v>
+      </c>
+      <c r="B20" s="61" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="63" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="96" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" s="97" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" s="98" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="64">
+        <v>20</v>
+      </c>
+      <c r="B21" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="E21" t="s">
+        <v>223</v>
+      </c>
+      <c r="G21" s="96" t="s">
+        <v>208</v>
+      </c>
+      <c r="H21" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="I21" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="98" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="64">
+        <v>21</v>
+      </c>
+      <c r="B22" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="63" t="s">
+        <v>166</v>
+      </c>
+      <c r="E22" t="s">
+        <v>223</v>
+      </c>
+      <c r="G22" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="H22" s="97" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" s="97" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="98" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="64">
+        <v>22</v>
+      </c>
+      <c r="B23" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="E23" t="s">
+        <v>223</v>
+      </c>
+      <c r="G23" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="H23" s="97" t="s">
+        <v>210</v>
+      </c>
+      <c r="I23" s="97" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" s="98" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="64">
+        <v>23</v>
+      </c>
+      <c r="B24" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="96" t="s">
+        <v>213</v>
+      </c>
+      <c r="H24" s="97" t="s">
+        <v>212</v>
+      </c>
+      <c r="I24" s="97" t="s">
+        <v>187</v>
+      </c>
+      <c r="J24" s="98" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="64">
+        <v>24</v>
+      </c>
+      <c r="B25" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>223</v>
+      </c>
+      <c r="G25" s="96" t="s">
+        <v>214</v>
+      </c>
+      <c r="H25" s="97" t="s">
+        <v>209</v>
+      </c>
+      <c r="I25" s="97" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="98" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="64">
+        <v>25</v>
+      </c>
+      <c r="B26" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="E26" t="s">
+        <v>223</v>
+      </c>
+      <c r="G26" s="96" t="s">
+        <v>214</v>
+      </c>
+      <c r="H26" s="97" t="s">
+        <v>210</v>
+      </c>
+      <c r="I26" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="J26" s="98" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="64">
+        <v>26</v>
+      </c>
+      <c r="B27" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" s="63" t="s">
+        <v>164</v>
+      </c>
+      <c r="E27" t="s">
+        <v>223</v>
+      </c>
+      <c r="G27" s="99" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="100" t="s">
+        <v>212</v>
+      </c>
+      <c r="I27" s="100" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="101" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="64">
+        <v>27</v>
+      </c>
+      <c r="B28" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>223</v>
+      </c>
+      <c r="G28" s="102" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="103" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" s="103" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="104" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="64">
+        <v>28</v>
+      </c>
+      <c r="B29" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="63" t="s">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>223</v>
+      </c>
+      <c r="G29" s="105" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" s="106" t="s">
+        <v>217</v>
+      </c>
+      <c r="I29" s="106" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="107" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="64">
+        <v>29</v>
+      </c>
+      <c r="B30" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="63" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="105" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" s="106" t="s">
+        <v>218</v>
+      </c>
+      <c r="I30" s="106" t="s">
+        <v>219</v>
+      </c>
+      <c r="J30" s="107" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="64">
+        <v>30</v>
+      </c>
+      <c r="B31" s="60" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="105" t="s">
+        <v>221</v>
+      </c>
+      <c r="H31" s="106" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="106" t="s">
+        <v>139</v>
+      </c>
+      <c r="J31" s="107" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G32" s="105" t="s">
+        <v>221</v>
+      </c>
+      <c r="H32" s="106" t="s">
+        <v>217</v>
+      </c>
+      <c r="I32" s="106" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="107" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G33" s="108" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="109" t="s">
+        <v>218</v>
+      </c>
+      <c r="I33" s="109" t="s">
+        <v>219</v>
+      </c>
+      <c r="J33" s="110" t="s">
+        <v>220</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ECC840A-39FE-48EF-AC39-316EEDAB0404}">
   <sheetPr>
     <tabColor theme="5"/>
@@ -1529,16 +3570,16 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="44" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="44"/>
+      <c r="C8" s="44"/>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
@@ -1598,11 +3639,11 @@
       <c r="A15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
       <c r="E15" s="27" t="s">
         <v>21</v>
       </c>
@@ -1617,11 +3658,11 @@
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="42"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9">
         <v>34.56</v>
@@ -1635,11 +3676,11 @@
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
+      <c r="C17" s="43"/>
+      <c r="D17" s="43"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>100000</v>
@@ -1653,11 +3694,11 @@
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
       <c r="E18" s="9">
         <v>1000000</v>
       </c>
@@ -1673,11 +3714,11 @@
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="43" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>20</v>
@@ -1691,11 +3732,11 @@
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="31"/>
+      <c r="C20" s="42"/>
+      <c r="D20" s="42"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9">
         <v>29.12</v>
@@ -1709,11 +3750,11 @@
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="30" t="s">
+      <c r="B21" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
+      <c r="C21" s="43"/>
+      <c r="D21" s="43"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>46.73</v>
@@ -1728,11 +3769,11 @@
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="31"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9">
         <v>35.67</v>
@@ -1747,11 +3788,11 @@
       <c r="A23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="43" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
       <c r="E23" s="12">
         <v>3421.98</v>
       </c>
@@ -1767,11 +3808,11 @@
       <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
+      <c r="C24" s="42"/>
+      <c r="D24" s="42"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9">
         <v>200000</v>
@@ -1785,11 +3826,11 @@
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="30" t="s">
+      <c r="B25" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>150000</v>
@@ -1803,11 +3844,11 @@
       <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
+      <c r="C26" s="42"/>
+      <c r="D26" s="42"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
         <v>20</v>
@@ -1821,11 +3862,11 @@
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="30" t="s">
+      <c r="B27" s="43" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>45.23</v>
@@ -1839,11 +3880,11 @@
       <c r="A28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="31"/>
+      <c r="C28" s="42"/>
+      <c r="D28" s="42"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
         <f>1.05*200000</f>
@@ -1858,11 +3899,11 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="30" t="s">
+      <c r="B29" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12">
         <f>1.05*100000</f>
@@ -1877,11 +3918,11 @@
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="42"/>
       <c r="E30" s="9">
         <v>3421.98</v>
       </c>
@@ -1897,11 +3938,11 @@
       <c r="A31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="30" t="s">
+      <c r="B31" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="30"/>
-      <c r="D31" s="30"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>204.73</v>
@@ -1915,11 +3956,11 @@
       <c r="A32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="C32" s="42"/>
+      <c r="D32" s="42"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9">
         <v>63.29</v>
@@ -1933,11 +3974,11 @@
       <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="30" t="s">
+      <c r="B33" s="43" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="30"/>
-      <c r="D33" s="30"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>100000</v>
@@ -1951,11 +3992,11 @@
       <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="C34" s="42"/>
+      <c r="D34" s="42"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9">
         <v>100000</v>
@@ -1969,11 +4010,11 @@
       <c r="A35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="30" t="s">
+      <c r="B35" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>86.7</v>
@@ -2042,14 +4083,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B27:D27"/>
@@ -2064,6 +4097,14 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Space Station Aurora/Support_Excel.xlsx
+++ b/Space Station Aurora/Support_Excel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Space Station Aurora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4AA22D-D9CC-462A-8298-BA7786246F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A652C2-CC48-42D6-892C-EC072D63F824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="241">
   <si>
     <t>Square cells</t>
   </si>
@@ -714,13 +714,58 @@
     <t>keypad</t>
   </si>
   <si>
-    <t>v</t>
-  </si>
-  <si>
     <t>A0 → resistor → anode</t>
   </si>
   <si>
     <t>A1 → resistor → anode</t>
+  </si>
+  <si>
+    <t>5V rail → Capacitor</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>On position</t>
+  </si>
+  <si>
+    <t>Off position</t>
+  </si>
+  <si>
+    <t>80% position</t>
+  </si>
+  <si>
+    <t>20% position</t>
+  </si>
+  <si>
+    <t>60% position</t>
+  </si>
+  <si>
+    <t>led2</t>
+  </si>
+  <si>
+    <t>3 blinks</t>
+  </si>
+  <si>
+    <t>on for 4 seconds</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Puzzle1</t>
+  </si>
+  <si>
+    <t>Puzzle2</t>
+  </si>
+  <si>
+    <t>40% position</t>
+  </si>
+  <si>
+    <t>Press 8 - 5 - 3 - 6 - #</t>
+  </si>
+  <si>
+    <t>serov2</t>
   </si>
 </sst>
 </file>
@@ -1145,42 +1190,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1219,19 +1228,19 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1246,7 +1255,7 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1255,11 +1264,47 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1822,14 +1867,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="52">
+      <c r="B2" s="99">
         <v>4</v>
       </c>
-      <c r="C2" s="50">
+      <c r="C2" s="105">
         <v>3</v>
       </c>
-      <c r="D2" s="51"/>
-      <c r="E2" s="46">
+      <c r="D2" s="106"/>
+      <c r="E2" s="102">
         <v>1</v>
       </c>
       <c r="G2" s="34" t="s">
@@ -1852,10 +1897,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="52"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="46"/>
+      <c r="B3" s="99"/>
+      <c r="C3" s="105"/>
+      <c r="D3" s="106"/>
+      <c r="E3" s="102"/>
       <c r="G3" s="40">
         <v>1</v>
       </c>
@@ -1878,10 +1923,10 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="52"/>
+      <c r="B4" s="99"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
-      <c r="E4" s="46"/>
+      <c r="E4" s="102"/>
       <c r="G4" s="40">
         <v>2</v>
       </c>
@@ -1904,10 +1949,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="52"/>
+      <c r="B5" s="99"/>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
-      <c r="E5" s="46"/>
+      <c r="E5" s="102"/>
       <c r="G5" s="41">
         <v>3</v>
       </c>
@@ -1930,10 +1975,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="52"/>
+      <c r="B6" s="99"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="46"/>
+      <c r="E6" s="102"/>
       <c r="G6" s="33">
         <v>4</v>
       </c>
@@ -1956,12 +2001,12 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="52"/>
-      <c r="C7" s="53">
+      <c r="B7" s="99"/>
+      <c r="C7" s="100">
         <v>5</v>
       </c>
-      <c r="D7" s="52"/>
-      <c r="E7" s="46"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="102"/>
       <c r="G7" s="33">
         <v>5</v>
       </c>
@@ -1984,12 +2029,12 @@
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="48">
+      <c r="B8" s="101">
         <v>6</v>
       </c>
-      <c r="C8" s="53"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="46">
+      <c r="C8" s="100"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="102">
         <v>2</v>
       </c>
       <c r="G8" s="32">
@@ -2014,10 +2059,10 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="48"/>
+      <c r="B9" s="101"/>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
-      <c r="E9" s="46"/>
+      <c r="E9" s="102"/>
       <c r="G9" s="32">
         <v>7</v>
       </c>
@@ -2040,16 +2085,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="48"/>
+      <c r="B10" s="101"/>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
-      <c r="E10" s="46"/>
+      <c r="E10" s="102"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="48"/>
+      <c r="B11" s="101"/>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
-      <c r="E11" s="46"/>
+      <c r="E11" s="102"/>
       <c r="G11" s="37">
         <v>1</v>
       </c>
@@ -2066,16 +2111,16 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="48"/>
-      <c r="C12" s="47">
+      <c r="B12" s="101"/>
+      <c r="C12" s="103">
         <v>7</v>
       </c>
-      <c r="D12" s="48"/>
-      <c r="E12" s="46"/>
-      <c r="G12" s="49">
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+      <c r="G12" s="104">
         <v>3</v>
       </c>
-      <c r="H12" s="50"/>
+      <c r="H12" s="105"/>
       <c r="I12" s="30">
         <f>L5</f>
         <v>2</v>
@@ -2086,10 +2131,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="47"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="46"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="103"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="102"/>
       <c r="G13" s="39">
         <v>4</v>
       </c>
@@ -2121,14 +2166,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C2:D3"/>
     <mergeCell ref="B2:B7"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="B8:B13"/>
     <mergeCell ref="E2:E7"/>
     <mergeCell ref="E8:E13"/>
     <mergeCell ref="C12:D13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C2:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2146,297 +2191,297 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E1" s="54" t="s">
+      <c r="E1" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="54" t="s">
+      <c r="F1" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="G1" s="54" t="s">
+      <c r="G1" s="42" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="43" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="56">
+      <c r="B2" s="44">
         <v>1</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="D2" s="55" t="s">
+      <c r="D2" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="E2" s="57">
+      <c r="E2" s="45">
         <v>21.7</v>
       </c>
-      <c r="F2" s="57">
+      <c r="F2" s="45">
         <f>B2*E2</f>
         <v>21.7</v>
       </c>
-      <c r="G2" s="55" t="s">
+      <c r="G2" s="43" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="56">
+      <c r="B3" s="44">
         <v>1</v>
       </c>
-      <c r="C3" s="55" t="s">
+      <c r="C3" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="55" t="s">
+      <c r="D3" s="43" t="s">
         <v>80</v>
       </c>
-      <c r="E3" s="57">
+      <c r="E3" s="45">
         <v>5.08</v>
       </c>
-      <c r="F3" s="57">
+      <c r="F3" s="45">
         <f t="shared" ref="F3:F11" si="0">B3*E3</f>
         <v>5.08</v>
       </c>
-      <c r="G3" s="55" t="s">
+      <c r="G3" s="43" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="55" t="s">
+      <c r="A4" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="56">
+      <c r="B4" s="44">
         <v>4</v>
       </c>
-      <c r="C4" s="55" t="s">
+      <c r="C4" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="55" t="s">
+      <c r="D4" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="E4" s="57">
+      <c r="E4" s="45">
         <v>1.88</v>
       </c>
-      <c r="F4" s="57">
+      <c r="F4" s="45">
         <f t="shared" si="0"/>
         <v>7.52</v>
       </c>
-      <c r="G4" s="55" t="s">
+      <c r="G4" s="43" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="B5" s="56">
+      <c r="B5" s="44">
         <v>3</v>
       </c>
-      <c r="C5" s="55" t="s">
+      <c r="C5" s="43" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="55" t="s">
+      <c r="D5" s="43" t="s">
         <v>85</v>
       </c>
-      <c r="E5" s="57">
+      <c r="E5" s="45">
         <v>0.93</v>
       </c>
-      <c r="F5" s="57">
+      <c r="F5" s="45">
         <f t="shared" si="0"/>
         <v>2.79</v>
       </c>
-      <c r="G5" s="55" t="s">
+      <c r="G5" s="43" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="56">
+      <c r="B6" s="44">
         <v>2</v>
       </c>
-      <c r="C6" s="55" t="s">
+      <c r="C6" s="43" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="43" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="57">
+      <c r="E6" s="45">
         <v>0.79</v>
       </c>
-      <c r="F6" s="57">
+      <c r="F6" s="45">
         <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="43" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="56">
+      <c r="B7" s="44">
         <v>2</v>
       </c>
-      <c r="C7" s="55" t="s">
+      <c r="C7" s="43" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="E7" s="57">
+      <c r="E7" s="45">
         <v>6.21</v>
       </c>
-      <c r="F7" s="57">
+      <c r="F7" s="45">
         <f t="shared" si="0"/>
         <v>12.42</v>
       </c>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="43" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="43" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="56">
+      <c r="B8" s="44">
         <v>1</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="55" t="s">
+      <c r="D8" s="43" t="s">
         <v>105</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="45">
         <v>4.58</v>
       </c>
-      <c r="F8" s="57">
+      <c r="F8" s="45">
         <f t="shared" si="0"/>
         <v>4.58</v>
       </c>
-      <c r="G8" s="55" t="s">
+      <c r="G8" s="43" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="B9" s="56">
+      <c r="B9" s="44">
         <v>1</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="43" t="s">
         <v>108</v>
       </c>
-      <c r="D9" s="55" t="s">
+      <c r="D9" s="43" t="s">
         <v>109</v>
       </c>
-      <c r="E9" s="57">
+      <c r="E9" s="45">
         <v>6.13</v>
       </c>
-      <c r="F9" s="57">
+      <c r="F9" s="45">
         <f t="shared" si="0"/>
         <v>6.13</v>
       </c>
-      <c r="G9" s="55" t="s">
+      <c r="G9" s="43" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="B10" s="56">
+      <c r="B10" s="44">
         <v>1</v>
       </c>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="55" t="s">
+      <c r="D10" s="43" t="s">
         <v>112</v>
       </c>
-      <c r="E10" s="57">
+      <c r="E10" s="45">
         <v>6.89</v>
       </c>
-      <c r="F10" s="57">
+      <c r="F10" s="45">
         <f t="shared" si="0"/>
         <v>6.89</v>
       </c>
-      <c r="G10" s="55" t="s">
+      <c r="G10" s="43" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="56">
+      <c r="B11" s="44">
         <v>1</v>
       </c>
-      <c r="C11" s="55" t="s">
+      <c r="C11" s="43" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="55" t="s">
+      <c r="D11" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="E11" s="57">
+      <c r="E11" s="45">
         <v>14.49</v>
       </c>
-      <c r="F11" s="57">
+      <c r="F11" s="45">
         <f t="shared" si="0"/>
         <v>14.49</v>
       </c>
-      <c r="G11" s="55" t="s">
+      <c r="G11" s="43" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="55"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="57"/>
-      <c r="F12" s="57"/>
-      <c r="G12" s="55"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="44"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="43"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="43"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="55"/>
-      <c r="B13" s="56"/>
-      <c r="C13" s="55"/>
-      <c r="D13" s="55"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="55"/>
+      <c r="A13" s="43"/>
+      <c r="B13" s="44"/>
+      <c r="C13" s="43"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="43"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="55"/>
-      <c r="B14" s="56"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="55"/>
+      <c r="A14" s="43"/>
+      <c r="B14" s="44"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="43"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="43"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F15" s="58">
+      <c r="F15" s="46">
         <f>SUM(F2:F14)</f>
         <v>83.179999999999993</v>
       </c>
@@ -2447,178 +2492,178 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="54" t="s">
+      <c r="A19" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="54" t="s">
+      <c r="B19" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="54" t="s">
+      <c r="C19" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="54" t="s">
+      <c r="D19" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="54" t="s">
+      <c r="E19" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="54" t="s">
+      <c r="G19" s="42" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="55" t="s">
+      <c r="A20" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="56">
+      <c r="B20" s="44">
         <v>4</v>
       </c>
-      <c r="C20" s="55" t="s">
+      <c r="C20" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="55" t="s">
+      <c r="D20" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="57">
+      <c r="E20" s="45">
         <v>0.89</v>
       </c>
-      <c r="F20" s="57"/>
-      <c r="G20" s="55" t="s">
+      <c r="F20" s="45"/>
+      <c r="G20" s="43" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="55" t="s">
+      <c r="A21" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="56">
+      <c r="B21" s="44">
         <v>1</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="C21" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="55" t="s">
+      <c r="D21" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="57">
+      <c r="E21" s="45">
         <v>1.07</v>
       </c>
-      <c r="F21" s="57"/>
-      <c r="G21" s="55"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="43"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="55"/>
-      <c r="B22" s="56"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="55"/>
-      <c r="E22" s="57"/>
-      <c r="F22" s="57"/>
-      <c r="G22" s="55"/>
+      <c r="A22" s="43"/>
+      <c r="B22" s="44"/>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="43"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="55"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="55"/>
-      <c r="E23" s="57"/>
-      <c r="F23" s="57"/>
-      <c r="G23" s="55"/>
+      <c r="A23" s="43"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="43"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="55"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="55"/>
-      <c r="D24" s="55"/>
-      <c r="E24" s="57"/>
-      <c r="F24" s="57"/>
-      <c r="G24" s="55"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="43"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="55"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="55"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="43"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="55"/>
-      <c r="B26" s="56"/>
-      <c r="C26" s="55"/>
-      <c r="D26" s="55"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="55"/>
+      <c r="A26" s="43"/>
+      <c r="B26" s="44"/>
+      <c r="C26" s="43"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="43"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="55"/>
-      <c r="B27" s="56"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="57"/>
-      <c r="F27" s="57"/>
-      <c r="G27" s="55"/>
+      <c r="A27" s="43"/>
+      <c r="B27" s="44"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="45"/>
+      <c r="F27" s="45"/>
+      <c r="G27" s="43"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="55"/>
-      <c r="B28" s="56"/>
-      <c r="C28" s="55"/>
-      <c r="D28" s="55"/>
-      <c r="E28" s="57"/>
-      <c r="F28" s="57"/>
-      <c r="G28" s="55"/>
+      <c r="A28" s="43"/>
+      <c r="B28" s="44"/>
+      <c r="C28" s="43"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="43"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="55"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="55"/>
-      <c r="D29" s="55"/>
-      <c r="E29" s="57"/>
-      <c r="F29" s="57"/>
-      <c r="G29" s="55"/>
+      <c r="A29" s="43"/>
+      <c r="B29" s="44"/>
+      <c r="C29" s="43"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="43"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="55"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="55"/>
-      <c r="D30" s="55"/>
-      <c r="E30" s="57"/>
-      <c r="F30" s="57"/>
-      <c r="G30" s="55"/>
+      <c r="A30" s="43"/>
+      <c r="B30" s="44"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="43"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="55"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="55"/>
-      <c r="D31" s="55"/>
-      <c r="E31" s="57"/>
-      <c r="F31" s="57"/>
-      <c r="G31" s="55"/>
+      <c r="A31" s="43"/>
+      <c r="B31" s="44"/>
+      <c r="C31" s="43"/>
+      <c r="D31" s="43"/>
+      <c r="E31" s="45"/>
+      <c r="F31" s="45"/>
+      <c r="G31" s="43"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="55"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="55"/>
-      <c r="D32" s="55"/>
-      <c r="E32" s="57"/>
-      <c r="F32" s="57"/>
-      <c r="G32" s="55"/>
+      <c r="A32" s="43"/>
+      <c r="B32" s="44"/>
+      <c r="C32" s="43"/>
+      <c r="D32" s="43"/>
+      <c r="E32" s="45"/>
+      <c r="F32" s="45"/>
+      <c r="G32" s="43"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="55"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="55"/>
-      <c r="D33" s="55"/>
-      <c r="E33" s="57"/>
-      <c r="F33" s="57"/>
-      <c r="G33" s="55"/>
+      <c r="A33" s="43"/>
+      <c r="B33" s="44"/>
+      <c r="C33" s="43"/>
+      <c r="D33" s="43"/>
+      <c r="E33" s="45"/>
+      <c r="F33" s="45"/>
+      <c r="G33" s="43"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F34" s="58">
+      <c r="F34" s="46">
         <f>SUM(F20:F33)</f>
         <v>0</v>
       </c>
@@ -2630,7 +2675,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77460AD8-8752-4C96-A515-3367E229774E}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="30"/>
@@ -2643,888 +2688,1017 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="47" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="47" t="s">
         <v>124</v>
       </c>
-      <c r="G1" s="59" t="s">
+      <c r="G1" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="47" t="s">
         <v>180</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="47" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="64">
+      <c r="A2" s="52">
         <v>1</v>
       </c>
-      <c r="B2" s="60" t="s">
+      <c r="B2" s="48" t="s">
         <v>125</v>
       </c>
-      <c r="C2" s="65" t="s">
+      <c r="C2" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="D2" s="63" t="s">
+      <c r="D2" s="51" t="s">
         <v>127</v>
       </c>
-      <c r="G2" s="66" t="s">
+      <c r="G2" s="54" t="s">
         <v>182</v>
       </c>
-      <c r="H2" s="67" t="s">
+      <c r="H2" s="55" t="s">
         <v>183</v>
       </c>
-      <c r="I2" s="67" t="s">
+      <c r="I2" s="55" t="s">
         <v>203</v>
       </c>
-      <c r="J2" s="68" t="s">
+      <c r="J2" s="56" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="64">
+      <c r="A3" s="52">
         <v>2</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="49" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="65" t="s">
+      <c r="C3" s="53" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="63" t="s">
+      <c r="D3" s="51" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="69" t="s">
+      <c r="G3" s="57" t="s">
         <v>182</v>
       </c>
-      <c r="H3" s="70" t="s">
+      <c r="H3" s="58" t="s">
         <v>186</v>
       </c>
-      <c r="I3" s="70" t="s">
+      <c r="I3" s="58" t="s">
+        <v>225</v>
+      </c>
+      <c r="J3" s="59" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="52">
+        <v>3</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="53" t="s">
+        <v>132</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="60" t="s">
+        <v>182</v>
+      </c>
+      <c r="H4" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="52">
+        <v>4</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="53" t="s">
+        <v>134</v>
+      </c>
+      <c r="D5" s="51" t="s">
+        <v>135</v>
+      </c>
+      <c r="G5" s="54" t="s">
+        <v>191</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="55" t="s">
+        <v>201</v>
+      </c>
+      <c r="J5" s="56" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="52">
+        <v>5</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="53" t="s">
+        <v>136</v>
+      </c>
+      <c r="D6" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>186</v>
+      </c>
+      <c r="I6" s="58" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" s="59" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="52">
+        <v>6</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="D7" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G7" s="60" t="s">
+        <v>191</v>
+      </c>
+      <c r="H7" s="61" t="s">
+        <v>188</v>
+      </c>
+      <c r="I7" s="61" t="s">
+        <v>189</v>
+      </c>
+      <c r="J7" s="62" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="52">
+        <v>7</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C8" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="51" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="75" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="63" t="s">
+        <v>194</v>
+      </c>
+      <c r="I8" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="J8" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="52">
+        <v>8</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C9" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="D9" s="51" t="s">
+        <v>141</v>
+      </c>
+      <c r="G9" s="77" t="s">
+        <v>193</v>
+      </c>
+      <c r="H9" s="64" t="s">
+        <v>196</v>
+      </c>
+      <c r="I9" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="J9" s="78" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="52">
+        <v>9</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C10" s="53" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" s="51" t="s">
+        <v>143</v>
+      </c>
+      <c r="G10" s="77" t="s">
+        <v>197</v>
+      </c>
+      <c r="H10" s="64" t="s">
+        <v>194</v>
+      </c>
+      <c r="I10" s="64" t="s">
+        <v>224</v>
+      </c>
+      <c r="J10" s="78" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="52">
+        <v>10</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="G11" s="79" t="s">
+        <v>197</v>
+      </c>
+      <c r="H11" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>189</v>
+      </c>
+      <c r="J11" s="80" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="52">
+        <v>11</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>145</v>
+      </c>
+      <c r="G12" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="H12" s="67" t="s">
+        <v>198</v>
+      </c>
+      <c r="I12" s="67" t="s">
+        <v>163</v>
+      </c>
+      <c r="J12" s="68" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="52">
+        <v>12</v>
+      </c>
+      <c r="B13" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" s="53" t="s">
+        <v>147</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="G13" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="H13" s="70" t="s">
+        <v>199</v>
+      </c>
+      <c r="I13" s="70" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="52">
+        <v>13</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C14" s="53" t="s">
+        <v>149</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="H14" s="70" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="70" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="52">
+        <v>14</v>
+      </c>
+      <c r="B15" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C15" s="53" t="s">
+        <v>151</v>
+      </c>
+      <c r="D15" s="51" t="s">
+        <v>152</v>
+      </c>
+      <c r="G15" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="H15" s="70" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="70" t="s">
+        <v>184</v>
+      </c>
+      <c r="J15" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="52">
+        <v>15</v>
+      </c>
+      <c r="B16" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C16" s="53" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="51" t="s">
+        <v>154</v>
+      </c>
+      <c r="G16" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="H16" s="70" t="s">
+        <v>204</v>
+      </c>
+      <c r="I16" s="70" t="s">
+        <v>207</v>
+      </c>
+      <c r="J16" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="52">
+        <v>16</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" s="53" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="51" t="s">
+        <v>156</v>
+      </c>
+      <c r="G17" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="H17" s="70" t="s">
+        <v>205</v>
+      </c>
+      <c r="I17" s="70" t="s">
+        <v>171</v>
+      </c>
+      <c r="J17" s="71" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="52">
+        <v>17</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C18" s="53" t="s">
+        <v>157</v>
+      </c>
+      <c r="D18" s="51" t="s">
+        <v>158</v>
+      </c>
+      <c r="G18" s="72" t="s">
+        <v>222</v>
+      </c>
+      <c r="H18" s="73" t="s">
+        <v>206</v>
+      </c>
+      <c r="I18" s="73" t="s">
+        <v>172</v>
+      </c>
+      <c r="J18" s="74" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="52">
+        <v>18</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="53" t="s">
+        <v>159</v>
+      </c>
+      <c r="D19" s="51" t="s">
+        <v>160</v>
+      </c>
+      <c r="G19" s="81" t="s">
+        <v>208</v>
+      </c>
+      <c r="H19" s="82" t="s">
+        <v>209</v>
+      </c>
+      <c r="I19" s="82" t="s">
+        <v>189</v>
+      </c>
+      <c r="J19" s="83" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="52">
+        <v>19</v>
+      </c>
+      <c r="B20" s="49" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="53" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>162</v>
+      </c>
+      <c r="G20" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="H20" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="I20" s="85" t="s">
+        <v>142</v>
+      </c>
+      <c r="J20" s="86" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="52">
+        <v>20</v>
+      </c>
+      <c r="B21" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G21" s="84" t="s">
+        <v>208</v>
+      </c>
+      <c r="H21" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="I21" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="J3" s="71" t="s">
+      <c r="J21" s="86" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="64">
-        <v>3</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="D4" s="63" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="72" t="s">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="52">
+        <v>21</v>
+      </c>
+      <c r="B22" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C22" s="53" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="51" t="s">
+        <v>166</v>
+      </c>
+      <c r="G22" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="H22" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="I22" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="J22" s="86" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="52">
+        <v>22</v>
+      </c>
+      <c r="B23" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C23" s="53" t="s">
+        <v>167</v>
+      </c>
+      <c r="D23" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G23" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="H23" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="I23" s="85" t="s">
+        <v>144</v>
+      </c>
+      <c r="J23" s="86" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="52">
+        <v>23</v>
+      </c>
+      <c r="B24" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C24" s="53" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G24" s="84" t="s">
+        <v>213</v>
+      </c>
+      <c r="H24" s="85" t="s">
+        <v>212</v>
+      </c>
+      <c r="I24" s="85" t="s">
+        <v>187</v>
+      </c>
+      <c r="J24" s="86" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="52">
+        <v>24</v>
+      </c>
+      <c r="B25" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="53" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G25" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="H25" s="85" t="s">
+        <v>209</v>
+      </c>
+      <c r="I25" s="85" t="s">
+        <v>189</v>
+      </c>
+      <c r="J25" s="86" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="52">
+        <v>25</v>
+      </c>
+      <c r="B26" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" s="53" t="s">
+        <v>171</v>
+      </c>
+      <c r="D26" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G26" s="84" t="s">
+        <v>214</v>
+      </c>
+      <c r="H26" s="85" t="s">
+        <v>210</v>
+      </c>
+      <c r="I26" s="85" t="s">
+        <v>146</v>
+      </c>
+      <c r="J26" s="86" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="52">
+        <v>26</v>
+      </c>
+      <c r="B27" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="53" t="s">
+        <v>172</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="87" t="s">
+        <v>214</v>
+      </c>
+      <c r="H27" s="88" t="s">
+        <v>212</v>
+      </c>
+      <c r="I27" s="88" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="89" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="52">
+        <v>27</v>
+      </c>
+      <c r="B28" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C28" s="53" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G28" s="90" t="s">
+        <v>215</v>
+      </c>
+      <c r="H28" s="91" t="s">
+        <v>216</v>
+      </c>
+      <c r="I28" s="91" t="s">
+        <v>138</v>
+      </c>
+      <c r="J28" s="92" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="52">
+        <v>28</v>
+      </c>
+      <c r="B29" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C29" s="53" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>169</v>
+      </c>
+      <c r="G29" s="93" t="s">
+        <v>215</v>
+      </c>
+      <c r="H29" s="94" t="s">
+        <v>217</v>
+      </c>
+      <c r="I29" s="94" t="s">
+        <v>189</v>
+      </c>
+      <c r="J29" s="95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="52">
+        <v>29</v>
+      </c>
+      <c r="B30" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>175</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>176</v>
+      </c>
+      <c r="G30" s="93" t="s">
+        <v>215</v>
+      </c>
+      <c r="H30" s="94" t="s">
+        <v>218</v>
+      </c>
+      <c r="I30" s="94" t="s">
+        <v>219</v>
+      </c>
+      <c r="J30" s="95" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="52">
+        <v>30</v>
+      </c>
+      <c r="B31" s="48" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" s="53" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="51" t="s">
+        <v>178</v>
+      </c>
+      <c r="G31" s="93" t="s">
+        <v>221</v>
+      </c>
+      <c r="H31" s="94" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="J31" s="95" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G32" s="93" t="s">
+        <v>221</v>
+      </c>
+      <c r="H32" s="94" t="s">
+        <v>217</v>
+      </c>
+      <c r="I32" s="94" t="s">
+        <v>189</v>
+      </c>
+      <c r="J32" s="95" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G33" s="96" t="s">
+        <v>221</v>
+      </c>
+      <c r="H33" s="97" t="s">
+        <v>218</v>
+      </c>
+      <c r="I33" s="97" t="s">
+        <v>219</v>
+      </c>
+      <c r="J33" s="98" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B34" s="47" t="s">
+        <v>235</v>
+      </c>
+      <c r="C34" s="47" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="47" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B35" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D35" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B36" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" t="s">
+        <v>221</v>
+      </c>
+      <c r="D36" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B37" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C37" t="s">
+        <v>208</v>
+      </c>
+      <c r="D37" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B38" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C38" t="s">
+        <v>214</v>
+      </c>
+      <c r="D38" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B39" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C39" t="s">
+        <v>213</v>
+      </c>
+      <c r="D39" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B40" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B41" s="30" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" t="s">
         <v>182</v>
       </c>
-      <c r="H4" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="I4" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J4" s="74" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="64">
-        <v>4</v>
-      </c>
-      <c r="B5" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>134</v>
-      </c>
-      <c r="D5" s="63" t="s">
-        <v>135</v>
-      </c>
-      <c r="E5" t="s">
-        <v>223</v>
-      </c>
-      <c r="G5" s="66" t="s">
-        <v>191</v>
-      </c>
-      <c r="H5" s="67" t="s">
-        <v>183</v>
-      </c>
-      <c r="I5" s="67" t="s">
-        <v>201</v>
-      </c>
-      <c r="J5" s="68" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="64">
-        <v>5</v>
-      </c>
-      <c r="B6" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>136</v>
-      </c>
-      <c r="D6" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" t="s">
-        <v>223</v>
-      </c>
-      <c r="G6" s="69" t="s">
-        <v>191</v>
-      </c>
-      <c r="H6" s="70" t="s">
-        <v>186</v>
-      </c>
-      <c r="I6" s="70" t="s">
-        <v>187</v>
-      </c>
-      <c r="J6" s="71" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="64">
-        <v>6</v>
-      </c>
-      <c r="B7" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C7" s="65" t="s">
-        <v>138</v>
-      </c>
-      <c r="D7" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" t="s">
-        <v>223</v>
-      </c>
-      <c r="G7" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="H7" s="73" t="s">
-        <v>188</v>
-      </c>
-      <c r="I7" s="73" t="s">
-        <v>189</v>
-      </c>
-      <c r="J7" s="74" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="64">
-        <v>7</v>
-      </c>
-      <c r="B8" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="65" t="s">
-        <v>139</v>
-      </c>
-      <c r="D8" s="63" t="s">
-        <v>137</v>
-      </c>
-      <c r="E8" t="s">
-        <v>223</v>
-      </c>
-      <c r="G8" s="87" t="s">
-        <v>193</v>
-      </c>
-      <c r="H8" s="75" t="s">
-        <v>194</v>
-      </c>
-      <c r="I8" s="75" t="s">
-        <v>224</v>
-      </c>
-      <c r="J8" s="88" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="64">
-        <v>8</v>
-      </c>
-      <c r="B9" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C9" s="65" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="63" t="s">
-        <v>141</v>
-      </c>
-      <c r="G9" s="89" t="s">
-        <v>193</v>
-      </c>
-      <c r="H9" s="76" t="s">
-        <v>196</v>
-      </c>
-      <c r="I9" s="76" t="s">
-        <v>189</v>
-      </c>
-      <c r="J9" s="90" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="64">
-        <v>9</v>
-      </c>
-      <c r="B10" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C10" s="65" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" s="63" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" t="s">
-        <v>223</v>
-      </c>
-      <c r="G10" s="89" t="s">
-        <v>197</v>
-      </c>
-      <c r="H10" s="76" t="s">
-        <v>194</v>
-      </c>
-      <c r="I10" s="76" t="s">
-        <v>225</v>
-      </c>
-      <c r="J10" s="90" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="64">
-        <v>10</v>
-      </c>
-      <c r="B11" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>144</v>
-      </c>
-      <c r="D11" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="E11" t="s">
-        <v>223</v>
-      </c>
-      <c r="G11" s="91" t="s">
-        <v>197</v>
-      </c>
-      <c r="H11" s="77" t="s">
-        <v>196</v>
-      </c>
-      <c r="I11" s="77" t="s">
-        <v>189</v>
-      </c>
-      <c r="J11" s="92" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="64">
-        <v>11</v>
-      </c>
-      <c r="B12" s="62" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="65" t="s">
-        <v>146</v>
-      </c>
-      <c r="D12" s="63" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" t="s">
-        <v>223</v>
-      </c>
-      <c r="G12" s="78" t="s">
+      <c r="D41" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B42" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C42" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B43" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C43" t="s">
+        <v>221</v>
+      </c>
+      <c r="D43" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B44" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C44" t="s">
+        <v>208</v>
+      </c>
+      <c r="D44" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B45" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C45" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B46" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C46" t="s">
+        <v>213</v>
+      </c>
+      <c r="D46" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B47" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" t="s">
         <v>222</v>
       </c>
-      <c r="H12" s="79" t="s">
-        <v>198</v>
-      </c>
-      <c r="I12" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="J12" s="80" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="64">
-        <v>12</v>
-      </c>
-      <c r="B13" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C13" s="65" t="s">
-        <v>147</v>
-      </c>
-      <c r="D13" s="63" t="s">
-        <v>148</v>
-      </c>
-      <c r="G13" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="H13" s="82" t="s">
-        <v>199</v>
-      </c>
-      <c r="I13" s="82" t="s">
-        <v>192</v>
-      </c>
-      <c r="J13" s="83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" s="64">
-        <v>13</v>
-      </c>
-      <c r="B14" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C14" s="65" t="s">
-        <v>149</v>
-      </c>
-      <c r="D14" s="63" t="s">
-        <v>150</v>
-      </c>
-      <c r="G14" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="H14" s="82" t="s">
-        <v>200</v>
-      </c>
-      <c r="I14" s="82" t="s">
-        <v>167</v>
-      </c>
-      <c r="J14" s="83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="64">
-        <v>14</v>
-      </c>
-      <c r="B15" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>151</v>
-      </c>
-      <c r="D15" s="63" t="s">
-        <v>152</v>
-      </c>
-      <c r="G15" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="H15" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="I15" s="82" t="s">
-        <v>184</v>
-      </c>
-      <c r="J15" s="83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="64">
-        <v>15</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C16" s="65" t="s">
-        <v>153</v>
-      </c>
-      <c r="D16" s="63" t="s">
-        <v>154</v>
-      </c>
-      <c r="G16" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="H16" s="82" t="s">
-        <v>204</v>
-      </c>
-      <c r="I16" s="82" t="s">
-        <v>207</v>
-      </c>
-      <c r="J16" s="83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="64">
-        <v>16</v>
-      </c>
-      <c r="B17" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" s="65" t="s">
-        <v>155</v>
-      </c>
-      <c r="D17" s="63" t="s">
-        <v>156</v>
-      </c>
-      <c r="G17" s="81" t="s">
-        <v>222</v>
-      </c>
-      <c r="H17" s="82" t="s">
-        <v>205</v>
-      </c>
-      <c r="I17" s="82" t="s">
-        <v>171</v>
-      </c>
-      <c r="J17" s="83" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="64">
-        <v>17</v>
-      </c>
-      <c r="B18" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C18" s="65" t="s">
-        <v>157</v>
-      </c>
-      <c r="D18" s="63" t="s">
-        <v>158</v>
-      </c>
-      <c r="G18" s="84" t="s">
-        <v>222</v>
-      </c>
-      <c r="H18" s="85" t="s">
-        <v>206</v>
-      </c>
-      <c r="I18" s="85" t="s">
-        <v>172</v>
-      </c>
-      <c r="J18" s="86" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="64">
-        <v>18</v>
-      </c>
-      <c r="B19" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C19" s="65" t="s">
-        <v>159</v>
-      </c>
-      <c r="D19" s="63" t="s">
-        <v>160</v>
-      </c>
-      <c r="G19" s="93" t="s">
-        <v>208</v>
-      </c>
-      <c r="H19" s="94" t="s">
-        <v>209</v>
-      </c>
-      <c r="I19" s="94" t="s">
-        <v>189</v>
-      </c>
-      <c r="J19" s="95" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="64">
-        <v>19</v>
-      </c>
-      <c r="B20" s="61" t="s">
-        <v>128</v>
-      </c>
-      <c r="C20" s="65" t="s">
-        <v>161</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>162</v>
-      </c>
-      <c r="G20" s="96" t="s">
-        <v>208</v>
-      </c>
-      <c r="H20" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="I20" s="97" t="s">
-        <v>142</v>
-      </c>
-      <c r="J20" s="98" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="64">
-        <v>20</v>
-      </c>
-      <c r="B21" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C21" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" t="s">
-        <v>223</v>
-      </c>
-      <c r="G21" s="96" t="s">
-        <v>208</v>
-      </c>
-      <c r="H21" s="97" t="s">
-        <v>212</v>
-      </c>
-      <c r="I21" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="J21" s="98" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="64">
-        <v>21</v>
-      </c>
-      <c r="B22" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C22" s="65" t="s">
-        <v>165</v>
-      </c>
-      <c r="D22" s="63" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" t="s">
-        <v>223</v>
-      </c>
-      <c r="G22" s="96" t="s">
-        <v>213</v>
-      </c>
-      <c r="H22" s="97" t="s">
-        <v>209</v>
-      </c>
-      <c r="I22" s="97" t="s">
-        <v>189</v>
-      </c>
-      <c r="J22" s="98" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="64">
-        <v>22</v>
-      </c>
-      <c r="B23" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C23" s="65" t="s">
-        <v>167</v>
-      </c>
-      <c r="D23" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E23" t="s">
-        <v>223</v>
-      </c>
-      <c r="G23" s="96" t="s">
-        <v>213</v>
-      </c>
-      <c r="H23" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="I23" s="97" t="s">
-        <v>144</v>
-      </c>
-      <c r="J23" s="98" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="64">
-        <v>23</v>
-      </c>
-      <c r="B24" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C24" s="65" t="s">
-        <v>168</v>
-      </c>
-      <c r="D24" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="E24" t="s">
-        <v>223</v>
-      </c>
-      <c r="G24" s="96" t="s">
-        <v>213</v>
-      </c>
-      <c r="H24" s="97" t="s">
-        <v>212</v>
-      </c>
-      <c r="I24" s="97" t="s">
-        <v>187</v>
-      </c>
-      <c r="J24" s="98" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="64">
-        <v>24</v>
-      </c>
-      <c r="B25" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C25" s="65" t="s">
-        <v>170</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="E25" t="s">
-        <v>223</v>
-      </c>
-      <c r="G25" s="96" t="s">
-        <v>214</v>
-      </c>
-      <c r="H25" s="97" t="s">
-        <v>209</v>
-      </c>
-      <c r="I25" s="97" t="s">
-        <v>189</v>
-      </c>
-      <c r="J25" s="98" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="64">
-        <v>25</v>
-      </c>
-      <c r="B26" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="65" t="s">
-        <v>171</v>
-      </c>
-      <c r="D26" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E26" t="s">
-        <v>223</v>
-      </c>
-      <c r="G26" s="96" t="s">
-        <v>214</v>
-      </c>
-      <c r="H26" s="97" t="s">
-        <v>210</v>
-      </c>
-      <c r="I26" s="97" t="s">
-        <v>146</v>
-      </c>
-      <c r="J26" s="98" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="64">
-        <v>26</v>
-      </c>
-      <c r="B27" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="65" t="s">
-        <v>172</v>
-      </c>
-      <c r="D27" s="63" t="s">
-        <v>164</v>
-      </c>
-      <c r="E27" t="s">
-        <v>223</v>
-      </c>
-      <c r="G27" s="99" t="s">
-        <v>214</v>
-      </c>
-      <c r="H27" s="100" t="s">
-        <v>212</v>
-      </c>
-      <c r="I27" s="100" t="s">
-        <v>187</v>
-      </c>
-      <c r="J27" s="101" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="64">
-        <v>27</v>
-      </c>
-      <c r="B28" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C28" s="65" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="E28" t="s">
-        <v>223</v>
-      </c>
-      <c r="G28" s="102" t="s">
-        <v>215</v>
-      </c>
-      <c r="H28" s="103" t="s">
-        <v>216</v>
-      </c>
-      <c r="I28" s="103" t="s">
-        <v>138</v>
-      </c>
-      <c r="J28" s="104" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="64">
-        <v>28</v>
-      </c>
-      <c r="B29" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C29" s="65" t="s">
-        <v>174</v>
-      </c>
-      <c r="D29" s="63" t="s">
-        <v>169</v>
-      </c>
-      <c r="E29" t="s">
-        <v>223</v>
-      </c>
-      <c r="G29" s="105" t="s">
-        <v>215</v>
-      </c>
-      <c r="H29" s="106" t="s">
-        <v>217</v>
-      </c>
-      <c r="I29" s="106" t="s">
-        <v>189</v>
-      </c>
-      <c r="J29" s="107" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="64">
-        <v>29</v>
-      </c>
-      <c r="B30" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C30" s="65" t="s">
-        <v>175</v>
-      </c>
-      <c r="D30" s="63" t="s">
-        <v>176</v>
-      </c>
-      <c r="G30" s="105" t="s">
-        <v>215</v>
-      </c>
-      <c r="H30" s="106" t="s">
-        <v>218</v>
-      </c>
-      <c r="I30" s="106" t="s">
-        <v>219</v>
-      </c>
-      <c r="J30" s="107" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="64">
-        <v>30</v>
-      </c>
-      <c r="B31" s="60" t="s">
-        <v>125</v>
-      </c>
-      <c r="C31" s="65" t="s">
-        <v>177</v>
-      </c>
-      <c r="D31" s="63" t="s">
-        <v>178</v>
-      </c>
-      <c r="G31" s="105" t="s">
-        <v>221</v>
-      </c>
-      <c r="H31" s="106" t="s">
-        <v>216</v>
-      </c>
-      <c r="I31" s="106" t="s">
-        <v>139</v>
-      </c>
-      <c r="J31" s="107" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G32" s="105" t="s">
-        <v>221</v>
-      </c>
-      <c r="H32" s="106" t="s">
-        <v>217</v>
-      </c>
-      <c r="I32" s="106" t="s">
-        <v>189</v>
-      </c>
-      <c r="J32" s="107" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="33" spans="7:10" x14ac:dyDescent="0.25">
-      <c r="G33" s="108" t="s">
-        <v>221</v>
-      </c>
-      <c r="H33" s="109" t="s">
-        <v>218</v>
-      </c>
-      <c r="I33" s="109" t="s">
-        <v>219</v>
-      </c>
-      <c r="J33" s="110" t="s">
-        <v>220</v>
+      <c r="D47" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B48" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C48" t="s">
+        <v>232</v>
+      </c>
+      <c r="D48" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="C49" t="s">
+        <v>240</v>
+      </c>
+      <c r="D49" t="s">
+        <v>234</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3570,16 +3744,16 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="44" t="s">
+      <c r="A7" s="109" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="44"/>
-      <c r="C7" s="44"/>
+      <c r="B7" s="109"/>
+      <c r="C7" s="109"/>
     </row>
     <row r="8" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44"/>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
+      <c r="A8" s="109"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="109"/>
       <c r="F8" s="7" t="s">
         <v>47</v>
       </c>
@@ -3639,11 +3813,11 @@
       <c r="A15" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B15" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
       <c r="E15" s="27" t="s">
         <v>21</v>
       </c>
@@ -3658,11 +3832,11 @@
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9">
         <v>34.56</v>
@@ -3676,11 +3850,11 @@
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="43"/>
-      <c r="D17" s="43"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>100000</v>
@@ -3694,11 +3868,11 @@
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="42" t="s">
+      <c r="B18" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="42"/>
-      <c r="D18" s="42"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
       <c r="E18" s="9">
         <v>1000000</v>
       </c>
@@ -3714,11 +3888,11 @@
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>20</v>
@@ -3732,11 +3906,11 @@
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="42" t="s">
+      <c r="B20" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="42"/>
-      <c r="D20" s="42"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9">
         <v>29.12</v>
@@ -3750,11 +3924,11 @@
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="43" t="s">
+      <c r="B21" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="43"/>
-      <c r="D21" s="43"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>46.73</v>
@@ -3769,11 +3943,11 @@
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9">
         <v>35.67</v>
@@ -3788,11 +3962,11 @@
       <c r="A23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="43" t="s">
+      <c r="B23" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="12">
         <v>3421.98</v>
       </c>
@@ -3808,11 +3982,11 @@
       <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="42" t="s">
+      <c r="B24" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="42"/>
-      <c r="D24" s="42"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9">
         <v>200000</v>
@@ -3826,11 +4000,11 @@
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="43" t="s">
+      <c r="B25" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>150000</v>
@@ -3844,11 +4018,11 @@
       <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="42" t="s">
+      <c r="B26" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="42"/>
-      <c r="D26" s="42"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
         <v>20</v>
@@ -3862,11 +4036,11 @@
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>45.23</v>
@@ -3880,11 +4054,11 @@
       <c r="A28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="42" t="s">
+      <c r="B28" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="42"/>
-      <c r="D28" s="42"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
         <f>1.05*200000</f>
@@ -3899,11 +4073,11 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="43" t="s">
+      <c r="B29" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12">
         <f>1.05*100000</f>
@@ -3918,11 +4092,11 @@
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="42"/>
-      <c r="D30" s="42"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
       <c r="E30" s="9">
         <v>3421.98</v>
       </c>
@@ -3938,11 +4112,11 @@
       <c r="A31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="43" t="s">
+      <c r="B31" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>204.73</v>
@@ -3956,11 +4130,11 @@
       <c r="A32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="42" t="s">
+      <c r="B32" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="42"/>
-      <c r="D32" s="42"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9">
         <v>63.29</v>
@@ -3974,11 +4148,11 @@
       <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="43" t="s">
+      <c r="B33" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>100000</v>
@@ -3992,11 +4166,11 @@
       <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="42"/>
-      <c r="D34" s="42"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9">
         <v>100000</v>
@@ -4010,11 +4184,11 @@
       <c r="A35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="43" t="s">
+      <c r="B35" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="43"/>
-      <c r="D35" s="43"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>86.7</v>
@@ -4083,6 +4257,14 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B27:D27"/>
@@ -4097,14 +4279,6 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Space Station Aurora/Support_Excel.xlsx
+++ b/Space Station Aurora/Support_Excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Space Station Aurora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64A652C2-CC48-42D6-892C-EC072D63F824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C64D84-3E6C-4959-86C1-40839BFD0A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -1093,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1269,6 +1269,15 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1284,25 +1293,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1324,6 +1331,72 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1552575</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4961E42-B7B1-6B6C-20CA-B84035D13C3C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm rot="16200000">
+          <a:off x="1724025" y="1419225"/>
+          <a:ext cx="4591050" cy="4933950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1867,14 +1940,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B2" s="99">
+      <c r="B2" s="102">
         <v>4</v>
       </c>
-      <c r="C2" s="105">
+      <c r="C2" s="100">
         <v>3</v>
       </c>
-      <c r="D2" s="106"/>
-      <c r="E2" s="102">
+      <c r="D2" s="101"/>
+      <c r="E2" s="105">
         <v>1</v>
       </c>
       <c r="G2" s="34" t="s">
@@ -1897,10 +1970,10 @@
       </c>
     </row>
     <row r="3" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B3" s="99"/>
-      <c r="C3" s="105"/>
-      <c r="D3" s="106"/>
-      <c r="E3" s="102"/>
+      <c r="B3" s="102"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="105"/>
       <c r="G3" s="40">
         <v>1</v>
       </c>
@@ -1923,10 +1996,10 @@
       </c>
     </row>
     <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="99"/>
+      <c r="B4" s="102"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
-      <c r="E4" s="102"/>
+      <c r="E4" s="105"/>
       <c r="G4" s="40">
         <v>2</v>
       </c>
@@ -1949,10 +2022,10 @@
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="99"/>
+      <c r="B5" s="102"/>
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
-      <c r="E5" s="102"/>
+      <c r="E5" s="105"/>
       <c r="G5" s="41">
         <v>3</v>
       </c>
@@ -1975,10 +2048,10 @@
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="99"/>
+      <c r="B6" s="102"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
-      <c r="E6" s="102"/>
+      <c r="E6" s="105"/>
       <c r="G6" s="33">
         <v>4</v>
       </c>
@@ -2001,12 +2074,12 @@
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="99"/>
-      <c r="C7" s="100">
+      <c r="B7" s="102"/>
+      <c r="C7" s="103">
         <v>5</v>
       </c>
-      <c r="D7" s="99"/>
-      <c r="E7" s="102"/>
+      <c r="D7" s="102"/>
+      <c r="E7" s="105"/>
       <c r="G7" s="33">
         <v>5</v>
       </c>
@@ -2029,12 +2102,12 @@
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="101">
+      <c r="B8" s="104">
         <v>6</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="102">
+      <c r="C8" s="103"/>
+      <c r="D8" s="102"/>
+      <c r="E8" s="105">
         <v>2</v>
       </c>
       <c r="G8" s="32">
@@ -2059,10 +2132,10 @@
       </c>
     </row>
     <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="101"/>
+      <c r="B9" s="104"/>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
-      <c r="E9" s="102"/>
+      <c r="E9" s="105"/>
       <c r="G9" s="32">
         <v>7</v>
       </c>
@@ -2085,16 +2158,16 @@
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="101"/>
+      <c r="B10" s="104"/>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
-      <c r="E10" s="102"/>
+      <c r="E10" s="105"/>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="101"/>
+      <c r="B11" s="104"/>
       <c r="C11" s="35"/>
       <c r="D11" s="35"/>
-      <c r="E11" s="102"/>
+      <c r="E11" s="105"/>
       <c r="G11" s="37">
         <v>1</v>
       </c>
@@ -2111,16 +2184,16 @@
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="101"/>
-      <c r="C12" s="103">
+      <c r="B12" s="104"/>
+      <c r="C12" s="106">
         <v>7</v>
       </c>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-      <c r="G12" s="104">
+      <c r="D12" s="104"/>
+      <c r="E12" s="105"/>
+      <c r="G12" s="99">
         <v>3</v>
       </c>
-      <c r="H12" s="105"/>
+      <c r="H12" s="100"/>
       <c r="I12" s="30">
         <f>L5</f>
         <v>2</v>
@@ -2131,10 +2204,10 @@
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="101"/>
-      <c r="C13" s="103"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="102"/>
+      <c r="B13" s="104"/>
+      <c r="C13" s="106"/>
+      <c r="D13" s="104"/>
+      <c r="E13" s="105"/>
       <c r="G13" s="39">
         <v>4</v>
       </c>
@@ -2181,13 +2254,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37A425A6-023C-40DB-9218-09DD8A4595A3}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G60"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="36.28515625" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="7" max="7" width="80.7109375" customWidth="1"/>
+    <col min="7" max="7" width="52.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -2454,227 +2527,288 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="43"/>
-      <c r="B12" s="44"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="43"/>
-      <c r="E12" s="45"/>
-      <c r="F12" s="45"/>
-      <c r="G12" s="43"/>
+      <c r="A12" s="111"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
+      <c r="G12" s="111"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="43"/>
-      <c r="B13" s="44"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="45"/>
-      <c r="G13" s="43"/>
+      <c r="A13" s="111"/>
+      <c r="B13" s="112"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="111"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="43"/>
-      <c r="B14" s="44"/>
-      <c r="C14" s="43"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="43"/>
+      <c r="A14" s="111"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="111"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F15" s="46">
-        <f>SUM(F2:F14)</f>
-        <v>83.179999999999993</v>
-      </c>
+      <c r="A15" s="111"/>
+      <c r="B15" s="112"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="111"/>
+      <c r="E15" s="113"/>
+      <c r="F15" s="113"/>
+      <c r="G15" s="111"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="111"/>
+      <c r="B16" s="112"/>
+      <c r="C16" s="111"/>
+      <c r="D16" s="111"/>
+      <c r="E16" s="113"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="111"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="111"/>
+      <c r="B17" s="112"/>
+      <c r="C17" s="111"/>
+      <c r="D17" s="111"/>
+      <c r="E17" s="113"/>
+      <c r="F17" s="113"/>
+      <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="A18" s="111"/>
+      <c r="B18" s="112"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="111"/>
+      <c r="E18" s="113"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="111"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="111"/>
+      <c r="B19" s="112"/>
+      <c r="C19" s="111"/>
+      <c r="D19" s="111"/>
+      <c r="E19" s="113"/>
+      <c r="F19" s="113"/>
+      <c r="G19" s="111"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="111"/>
+      <c r="B20" s="112"/>
+      <c r="D20" s="111"/>
+      <c r="E20" s="113"/>
+      <c r="F20" s="113"/>
+      <c r="G20" s="111"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="111"/>
+      <c r="B21" s="112"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="111"/>
+      <c r="E21" s="113"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="42" t="s">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="42" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="42" t="s">
+      <c r="B45" s="42" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="42" t="s">
+      <c r="C45" s="42" t="s">
         <v>69</v>
       </c>
-      <c r="D19" s="42" t="s">
+      <c r="D45" s="42" t="s">
         <v>78</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E45" s="42" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F45" s="42" t="s">
         <v>84</v>
       </c>
-      <c r="G19" s="42" t="s">
+      <c r="G45" s="42" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="43" t="s">
         <v>89</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B46" s="44">
         <v>4</v>
       </c>
-      <c r="C20" s="43" t="s">
+      <c r="C46" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D46" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E46" s="45">
         <v>0.89</v>
       </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="43" t="s">
+      <c r="F46" s="45"/>
+      <c r="G46" s="43" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="43" t="s">
         <v>119</v>
       </c>
-      <c r="B21" s="44">
+      <c r="B47" s="44">
         <v>1</v>
       </c>
-      <c r="C21" s="43" t="s">
+      <c r="C47" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="43" t="s">
+      <c r="D47" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="E21" s="45">
+      <c r="E47" s="45">
         <v>1.07</v>
       </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="43"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="43"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="43"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="45"/>
-      <c r="F22" s="45"/>
-      <c r="G22" s="43"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="43"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="45"/>
-      <c r="F23" s="45"/>
-      <c r="G23" s="43"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="43"/>
-      <c r="D24" s="43"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="43"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="43"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="43"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="43"/>
-      <c r="D26" s="43"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="43"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="43"/>
-      <c r="E27" s="45"/>
-      <c r="F27" s="45"/>
-      <c r="G27" s="43"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="43"/>
-      <c r="D28" s="43"/>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="43"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="43"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="43"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="43"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="43"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="43"/>
-      <c r="B31" s="44"/>
-      <c r="C31" s="43"/>
-      <c r="D31" s="43"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="43"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="43"/>
-      <c r="B32" s="44"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="43"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="43"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="43"/>
-      <c r="B33" s="44"/>
-      <c r="C33" s="43"/>
-      <c r="D33" s="43"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="45"/>
-      <c r="G33" s="43"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F34" s="46">
-        <f>SUM(F20:F33)</f>
+      <c r="F47" s="45"/>
+      <c r="G47" s="43"/>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="43"/>
+      <c r="B48" s="44"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="43"/>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="43"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="43"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="43"/>
+      <c r="B50" s="44"/>
+      <c r="C50" s="43"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="45"/>
+      <c r="G50" s="43"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="43"/>
+      <c r="B51" s="44"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="45"/>
+      <c r="G51" s="43"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="43"/>
+      <c r="B52" s="44"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="43"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="43"/>
+      <c r="B53" s="44"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="43"/>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" s="43"/>
+      <c r="B54" s="44"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="45"/>
+      <c r="F54" s="45"/>
+      <c r="G54" s="43"/>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" s="43"/>
+      <c r="B55" s="44"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="45"/>
+      <c r="G55" s="43"/>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" s="43"/>
+      <c r="B56" s="44"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="45"/>
+      <c r="G56" s="43"/>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" s="43"/>
+      <c r="B57" s="44"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="45"/>
+      <c r="G57" s="43"/>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" s="43"/>
+      <c r="B58" s="44"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="45"/>
+      <c r="F58" s="45"/>
+      <c r="G58" s="43"/>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" s="43"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="45"/>
+      <c r="F59" s="45"/>
+      <c r="G59" s="43"/>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F60" s="46">
+        <f>SUM(F46:F59)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77460AD8-8752-4C96-A515-3367E229774E}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3700,6 +3834,7 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="55" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3832,11 +3967,11 @@
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="108" t="s">
+      <c r="B16" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9">
         <v>34.56</v>
@@ -3850,11 +3985,11 @@
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="107" t="s">
+      <c r="B17" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="107"/>
-      <c r="D17" s="107"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="108"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>100000</v>
@@ -3868,11 +4003,11 @@
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="108" t="s">
+      <c r="B18" s="107" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="108"/>
-      <c r="D18" s="108"/>
+      <c r="C18" s="107"/>
+      <c r="D18" s="107"/>
       <c r="E18" s="9">
         <v>1000000</v>
       </c>
@@ -3888,11 +4023,11 @@
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="107" t="s">
+      <c r="B19" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="108"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>20</v>
@@ -3906,11 +4041,11 @@
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="108" t="s">
+      <c r="B20" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="108"/>
-      <c r="D20" s="108"/>
+      <c r="C20" s="107"/>
+      <c r="D20" s="107"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9">
         <v>29.12</v>
@@ -3924,11 +4059,11 @@
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="107" t="s">
+      <c r="B21" s="108" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="107"/>
-      <c r="D21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="108"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>46.73</v>
@@ -3943,11 +4078,11 @@
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="108" t="s">
+      <c r="B22" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
+      <c r="C22" s="107"/>
+      <c r="D22" s="107"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9">
         <v>35.67</v>
@@ -3962,11 +4097,11 @@
       <c r="A23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="107" t="s">
+      <c r="B23" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
+      <c r="C23" s="108"/>
+      <c r="D23" s="108"/>
       <c r="E23" s="12">
         <v>3421.98</v>
       </c>
@@ -3982,11 +4117,11 @@
       <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="108" t="s">
+      <c r="B24" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="108"/>
-      <c r="D24" s="108"/>
+      <c r="C24" s="107"/>
+      <c r="D24" s="107"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9">
         <v>200000</v>
@@ -4000,11 +4135,11 @@
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="107" t="s">
+      <c r="B25" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="107"/>
-      <c r="D25" s="107"/>
+      <c r="C25" s="108"/>
+      <c r="D25" s="108"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>150000</v>
@@ -4018,11 +4153,11 @@
       <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="108" t="s">
+      <c r="B26" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="108"/>
-      <c r="D26" s="108"/>
+      <c r="C26" s="107"/>
+      <c r="D26" s="107"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
         <v>20</v>
@@ -4036,11 +4171,11 @@
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="107" t="s">
+      <c r="B27" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="107"/>
-      <c r="D27" s="107"/>
+      <c r="C27" s="108"/>
+      <c r="D27" s="108"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>45.23</v>
@@ -4054,11 +4189,11 @@
       <c r="A28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="108" t="s">
+      <c r="B28" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="108"/>
-      <c r="D28" s="108"/>
+      <c r="C28" s="107"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
         <f>1.05*200000</f>
@@ -4073,11 +4208,11 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="107" t="s">
+      <c r="B29" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="107"/>
-      <c r="D29" s="107"/>
+      <c r="C29" s="108"/>
+      <c r="D29" s="108"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12">
         <f>1.05*100000</f>
@@ -4092,11 +4227,11 @@
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="108" t="s">
+      <c r="B30" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="108"/>
-      <c r="D30" s="108"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
       <c r="E30" s="9">
         <v>3421.98</v>
       </c>
@@ -4112,11 +4247,11 @@
       <c r="A31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="107" t="s">
+      <c r="B31" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="107"/>
-      <c r="D31" s="107"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="108"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>204.73</v>
@@ -4130,11 +4265,11 @@
       <c r="A32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="108" t="s">
+      <c r="B32" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="108"/>
-      <c r="D32" s="108"/>
+      <c r="C32" s="107"/>
+      <c r="D32" s="107"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9">
         <v>63.29</v>
@@ -4148,11 +4283,11 @@
       <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="107" t="s">
+      <c r="B33" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="107"/>
-      <c r="D33" s="107"/>
+      <c r="C33" s="108"/>
+      <c r="D33" s="108"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>100000</v>
@@ -4166,11 +4301,11 @@
       <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="108" t="s">
+      <c r="B34" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="108"/>
-      <c r="D34" s="108"/>
+      <c r="C34" s="107"/>
+      <c r="D34" s="107"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9">
         <v>100000</v>
@@ -4184,11 +4319,11 @@
       <c r="A35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="107" t="s">
+      <c r="B35" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="107"/>
-      <c r="D35" s="107"/>
+      <c r="C35" s="108"/>
+      <c r="D35" s="108"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>86.7</v>
@@ -4257,14 +4392,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B27:D27"/>
@@ -4279,6 +4406,14 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:D28"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Space Station Aurora/Support_Excel.xlsx
+++ b/Space Station Aurora/Support_Excel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\EscapeBackpack\EscapeBackpack\Space Station Aurora\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C64D84-3E6C-4959-86C1-40839BFD0A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9F595C-BA49-41C1-B593-3EB83F86641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -1093,7 +1093,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1293,23 +1293,16 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1715,7 +1708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D260E2E-9366-4C07-AD85-6CF609B51D36}">
-  <dimension ref="A2:M20"/>
+  <dimension ref="A2:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
@@ -1917,6 +1910,40 @@
       <c r="E20">
         <f>C20-(2*C9)/10</f>
         <v>20.91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2340</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <f>A23/B23</f>
+        <v>156</v>
+      </c>
+      <c r="C24">
+        <f>B24+$B$24</f>
+        <v>312</v>
+      </c>
+      <c r="D24">
+        <f t="shared" ref="D24:G24" si="0">C24+$B$24</f>
+        <v>468</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="0"/>
+        <v>624</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>936</v>
       </c>
     </row>
   </sheetData>
@@ -2527,93 +2554,54 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="111"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="113"/>
-      <c r="F12" s="113"/>
-      <c r="G12" s="111"/>
+      <c r="B12" s="30"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="111"/>
-      <c r="B13" s="112"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="111"/>
+      <c r="B13" s="30"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="111"/>
-      <c r="B14" s="112"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="113"/>
-      <c r="G14" s="111"/>
+      <c r="B14" s="30"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="111"/>
-      <c r="B15" s="112"/>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="113"/>
-      <c r="G15" s="111"/>
+      <c r="B15" s="30"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="111"/>
-      <c r="B16" s="112"/>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="113"/>
-      <c r="G16" s="111"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="111"/>
-      <c r="B17" s="112"/>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="113"/>
-      <c r="G17" s="111"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="111"/>
-      <c r="B18" s="112"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="111"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="111"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="111"/>
-      <c r="B19" s="112"/>
-      <c r="C19" s="111"/>
-      <c r="D19" s="111"/>
-      <c r="E19" s="113"/>
-      <c r="F19" s="113"/>
-      <c r="G19" s="111"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="111"/>
-      <c r="B20" s="112"/>
-      <c r="D20" s="111"/>
-      <c r="E20" s="113"/>
-      <c r="F20" s="113"/>
-      <c r="G20" s="111"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="111"/>
-      <c r="B21" s="112"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="113"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
+      <c r="B16" s="30"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="30"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="30"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="30"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="30"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="46"/>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="30"/>
+      <c r="E21" s="46"/>
+      <c r="F21" s="46"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
@@ -3967,11 +3955,11 @@
       <c r="A16" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B16" s="107" t="s">
+      <c r="B16" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
       <c r="E16" s="9"/>
       <c r="F16" s="9">
         <v>34.56</v>
@@ -3985,11 +3973,11 @@
       <c r="A17" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="108" t="s">
+      <c r="B17" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="108"/>
-      <c r="D17" s="108"/>
+      <c r="C17" s="107"/>
+      <c r="D17" s="107"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12">
         <v>100000</v>
@@ -4003,11 +3991,11 @@
       <c r="A18" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="107" t="s">
+      <c r="B18" s="108" t="s">
         <v>32</v>
       </c>
-      <c r="C18" s="107"/>
-      <c r="D18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="108"/>
       <c r="E18" s="9">
         <v>1000000</v>
       </c>
@@ -4023,11 +4011,11 @@
       <c r="A19" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="108" t="s">
+      <c r="B19" s="107" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="108"/>
-      <c r="D19" s="108"/>
+      <c r="C19" s="107"/>
+      <c r="D19" s="107"/>
       <c r="E19" s="12"/>
       <c r="F19" s="12">
         <v>20</v>
@@ -4041,11 +4029,11 @@
       <c r="A20" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="107" t="s">
+      <c r="B20" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="107"/>
-      <c r="D20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="108"/>
       <c r="E20" s="9"/>
       <c r="F20" s="9">
         <v>29.12</v>
@@ -4059,11 +4047,11 @@
       <c r="A21" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="108" t="s">
+      <c r="B21" s="107" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="108"/>
-      <c r="D21" s="108"/>
+      <c r="C21" s="107"/>
+      <c r="D21" s="107"/>
       <c r="E21" s="12"/>
       <c r="F21" s="12">
         <v>46.73</v>
@@ -4078,11 +4066,11 @@
       <c r="A22" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="107" t="s">
+      <c r="B22" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="108"/>
       <c r="E22" s="9"/>
       <c r="F22" s="9">
         <v>35.67</v>
@@ -4097,11 +4085,11 @@
       <c r="A23" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="108" t="s">
+      <c r="B23" s="107" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="108"/>
-      <c r="D23" s="108"/>
+      <c r="C23" s="107"/>
+      <c r="D23" s="107"/>
       <c r="E23" s="12">
         <v>3421.98</v>
       </c>
@@ -4117,11 +4105,11 @@
       <c r="A24" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="107" t="s">
+      <c r="B24" s="108" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="108"/>
       <c r="E24" s="9"/>
       <c r="F24" s="9">
         <v>200000</v>
@@ -4135,11 +4123,11 @@
       <c r="A25" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="108" t="s">
+      <c r="B25" s="107" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="108"/>
-      <c r="D25" s="108"/>
+      <c r="C25" s="107"/>
+      <c r="D25" s="107"/>
       <c r="E25" s="12"/>
       <c r="F25" s="12">
         <v>150000</v>
@@ -4153,11 +4141,11 @@
       <c r="A26" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="107" t="s">
+      <c r="B26" s="108" t="s">
         <v>34</v>
       </c>
-      <c r="C26" s="107"/>
-      <c r="D26" s="107"/>
+      <c r="C26" s="108"/>
+      <c r="D26" s="108"/>
       <c r="E26" s="9"/>
       <c r="F26" s="9">
         <v>20</v>
@@ -4171,11 +4159,11 @@
       <c r="A27" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="108" t="s">
+      <c r="B27" s="107" t="s">
         <v>29</v>
       </c>
-      <c r="C27" s="108"/>
-      <c r="D27" s="108"/>
+      <c r="C27" s="107"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="12"/>
       <c r="F27" s="12">
         <v>45.23</v>
@@ -4189,11 +4177,11 @@
       <c r="A28" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B28" s="107" t="s">
+      <c r="B28" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="107"/>
-      <c r="D28" s="107"/>
+      <c r="C28" s="108"/>
+      <c r="D28" s="108"/>
       <c r="E28" s="9"/>
       <c r="F28" s="9">
         <f>1.05*200000</f>
@@ -4208,11 +4196,11 @@
       <c r="A29" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B29" s="108" t="s">
+      <c r="B29" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C29" s="108"/>
-      <c r="D29" s="108"/>
+      <c r="C29" s="107"/>
+      <c r="D29" s="107"/>
       <c r="E29" s="12"/>
       <c r="F29" s="12">
         <f>1.05*100000</f>
@@ -4227,11 +4215,11 @@
       <c r="A30" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="107" t="s">
+      <c r="B30" s="108" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="107"/>
-      <c r="D30" s="107"/>
+      <c r="C30" s="108"/>
+      <c r="D30" s="108"/>
       <c r="E30" s="9">
         <v>3421.98</v>
       </c>
@@ -4247,11 +4235,11 @@
       <c r="A31" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B31" s="108" t="s">
+      <c r="B31" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="108"/>
-      <c r="D31" s="108"/>
+      <c r="C31" s="107"/>
+      <c r="D31" s="107"/>
       <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>204.73</v>
@@ -4265,11 +4253,11 @@
       <c r="A32" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="107" t="s">
+      <c r="B32" s="108" t="s">
         <v>29</v>
       </c>
-      <c r="C32" s="107"/>
-      <c r="D32" s="107"/>
+      <c r="C32" s="108"/>
+      <c r="D32" s="108"/>
       <c r="E32" s="9"/>
       <c r="F32" s="9">
         <v>63.29</v>
@@ -4283,11 +4271,11 @@
       <c r="A33" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="108" t="s">
+      <c r="B33" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="108"/>
-      <c r="D33" s="108"/>
+      <c r="C33" s="107"/>
+      <c r="D33" s="107"/>
       <c r="E33" s="12"/>
       <c r="F33" s="12">
         <v>100000</v>
@@ -4301,11 +4289,11 @@
       <c r="A34" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="107" t="s">
+      <c r="B34" s="108" t="s">
         <v>31</v>
       </c>
-      <c r="C34" s="107"/>
-      <c r="D34" s="107"/>
+      <c r="C34" s="108"/>
+      <c r="D34" s="108"/>
       <c r="E34" s="9"/>
       <c r="F34" s="9">
         <v>100000</v>
@@ -4319,11 +4307,11 @@
       <c r="A35" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="108" t="s">
+      <c r="B35" s="107" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="108"/>
-      <c r="D35" s="108"/>
+      <c r="C35" s="107"/>
+      <c r="D35" s="107"/>
       <c r="E35" s="12"/>
       <c r="F35" s="12">
         <v>86.7</v>
@@ -4392,6 +4380,14 @@
     </row>
   </sheetData>
   <mergeCells count="22">
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A7:C8"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="B15:D15"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
     <mergeCell ref="B35:D35"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B27:D27"/>
@@ -4406,14 +4402,6 @@
     <mergeCell ref="B25:D25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="B28:D28"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="A7:C8"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
